--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20261005.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20261005.xlsx
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.7010362694300518</v>
+        <v>0.7018134715025908</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.1496321243523316</v>
+        <v>0.1504093264248705</v>
       </c>
     </row>
     <row r="8">
@@ -7575,17 +7575,17 @@
     <row r="66">
       <c r="A66" s="19" t="inlineStr">
         <is>
-          <t>P8 素案</t>
+          <t>P11 品質・進捗管理</t>
         </is>
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>8-9</t>
+          <t>11-3</t>
         </is>
       </c>
       <c r="C66" s="19" t="inlineStr">
         <is>
-          <t>素案の構成・体裁の点検（他団体の第10期計画との対比）</t>
+          <t>図表の追加作成</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="F66" s="20" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G66" s="23" t="inlineStr">
@@ -7609,16 +7609,16 @@
         </is>
       </c>
       <c r="H66" s="32" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="I66" s="32" t="n">
-        <v>37.8</v>
+        <v>28.1</v>
       </c>
       <c r="J66" s="32" t="n">
-        <v>47.2</v>
+        <v>51.9</v>
       </c>
       <c r="K66" s="20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L66" s="33" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="M66" s="19" t="inlineStr">
         <is>
-          <t>**残る未対応は、第5章の各施策の記載を5項目にそろえること、事業所調査（未実施。実施の可否を町と相談）、国の基本指針が示す確認すべき指標との対応表**</t>
+          <t>**残る2点はいずれも町データ待ち。地域ケア会議の開催回数・検討件数と、介護給付適正化の主要3事業の実施状況である**</t>
         </is>
       </c>
     </row>
@@ -7639,12 +7639,12 @@
       </c>
       <c r="B67" s="20" t="inlineStr">
         <is>
-          <t>11-3</t>
+          <t>11-4</t>
         </is>
       </c>
       <c r="C67" s="19" t="inlineStr">
         <is>
-          <t>図表の追加作成</t>
+          <t>成果品の体裁の統一と機械点検</t>
         </is>
       </c>
       <c r="D67" s="20" t="inlineStr">
@@ -7686,24 +7686,24 @@
       </c>
       <c r="M67" s="19" t="inlineStr">
         <is>
-          <t>**残る2点はいずれも町データ待ち。地域ケア会議の開催回数・検討件数と、介護給付適正化の主要3事業の実施状況である**</t>
+          <t>**印刷用の最終体裁（4色刷り・80頁）は組版工程（10-2）で別に点検する**</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="19" t="inlineStr">
         <is>
-          <t>P11 品質・進捗管理</t>
+          <t>P8 素案</t>
         </is>
       </c>
       <c r="B68" s="20" t="inlineStr">
         <is>
-          <t>11-4</t>
+          <t>8-1</t>
         </is>
       </c>
       <c r="C68" s="19" t="inlineStr">
         <is>
-          <t>成果品の体裁の統一と機械点検</t>
+          <t>素案の作成</t>
         </is>
       </c>
       <c r="D68" s="20" t="inlineStr">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="E68" s="20" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F68" s="20" t="inlineStr">
@@ -7727,16 +7727,16 @@
         </is>
       </c>
       <c r="H68" s="32" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="I68" s="32" t="n">
-        <v>28.1</v>
+        <v>42.8</v>
       </c>
       <c r="J68" s="32" t="n">
-        <v>51.9</v>
+        <v>52.2</v>
       </c>
       <c r="K68" s="20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L68" s="33" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="M68" s="19" t="inlineStr">
         <is>
-          <t>**印刷用の最終体裁（4色刷り・80頁）は組版工程（10-2）で別に点検する**</t>
+          <t>**9月24日に、受託者が算定すべき未確定箇所をすべて解消した。**所得段階別保険料率を13段階すべてについて算定し（乗率・年額・被保険者数・構成比）、必要利用定員総数・地域支援事業の量・認知症高齢者数を加えた。**未確定は158箇所→94箇所となり、【算定後に記載】は0件になった。****あわせて数値の誤りを2件正した。**①所得第2段階の乗率を年報 様式1 所得段階別の令和7年度の値により0.486としたが、**これは誤りで0.485が正しい**（9月25日に再訂正）。第9期計画本文が「基準額×0.485」「年額38,500円」と明記しており、79,200円×0.485＝38,412円の100円未満切上げで38,500円になる。年報の令和6年度は485であり、令和7年度の486が入力誤りである。②所得第1〜3段階の割合を28％としていたが、1,094人÷3,443人で31.8％が正しい。**第2章1の人口（見える化の将来推計・暦年）と第2章6の被保険者数（第10期将来推計用推計人口・年度）が別系列であることを注記した。**従前の注は「保険料算定との整合のため見える化の推計を用いる」と書いていたが、保険料算定は後者を用いており誤りであった</t>
         </is>
       </c>
     </row>
@@ -7757,12 +7757,12 @@
       </c>
       <c r="B69" s="20" t="inlineStr">
         <is>
-          <t>8-1</t>
+          <t>8-9</t>
         </is>
       </c>
       <c r="C69" s="19" t="inlineStr">
         <is>
-          <t>素案の作成</t>
+          <t>素案の構成・体裁の点検（他団体の第10期計画との対比）</t>
         </is>
       </c>
       <c r="D69" s="20" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="E69" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F69" s="20" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="G69" s="23" t="inlineStr">
@@ -7786,16 +7786,16 @@
         </is>
       </c>
       <c r="H69" s="32" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="I69" s="32" t="n">
-        <v>42.8</v>
+        <v>37.8</v>
       </c>
       <c r="J69" s="32" t="n">
         <v>52.2</v>
       </c>
       <c r="K69" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L69" s="33" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="M69" s="19" t="inlineStr">
         <is>
-          <t>**9月24日に、受託者が算定すべき未確定箇所をすべて解消した。**所得段階別保険料率を13段階すべてについて算定し（乗率・年額・被保険者数・構成比）、必要利用定員総数・地域支援事業の量・認知症高齢者数を加えた。**未確定は158箇所→94箇所となり、【算定後に記載】は0件になった。****あわせて数値の誤りを2件正した。**①所得第2段階の乗率を年報 様式1 所得段階別の令和7年度の値により0.486としたが、**これは誤りで0.485が正しい**（9月25日に再訂正）。第9期計画本文が「基準額×0.485」「年額38,500円」と明記しており、79,200円×0.485＝38,412円の100円未満切上げで38,500円になる。年報の令和6年度は485であり、令和7年度の486が入力誤りである。②所得第1〜3段階の割合を28％としていたが、1,094人÷3,443人で31.8％が正しい。**第2章1の人口（見える化の将来推計・暦年）と第2章6の被保険者数（第10期将来推計用推計人口・年度）が別系列であることを注記した。**従前の注は「保険料算定との整合のため見える化の推計を用いる」と書いていたが、保険料算定は後者を用いており誤りであった</t>
+          <t>**残る未対応は、第5章の各施策の記載を5項目にそろえること、事業所調査（未実施。実施の可否を町と相談）、国の基本指針が示す確認すべき指標との対応表**</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8283,7 @@
     <row r="79">
       <c r="A79" s="34" t="inlineStr">
         <is>
-          <t>加重の実績進捗率 70.1％　対　予定進捗率 55.1％　乖離 +15.0ポイント</t>
+          <t>加重の実績進捗率 70.2％　対　予定進捗率 55.1％　乖離 +15.0ポイント</t>
         </is>
       </c>
     </row>
@@ -12849,14 +12849,14 @@
         </is>
       </c>
       <c r="L55" s="22" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="M55" s="23" t="n">
         <v>3</v>
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>**9月29日に、他団体の第10期計画の見出し129件を機械的に抽出し、小野町の素案と44項目で対比した（03_計画素案）。****○18件・△11件・×14件・該当なし1件で、うち16件を素案に反映済みである。**第1章に3節（計画策定の視点／日常生活圏域の設定／計画の進行管理・推進体制）、**第3章「第9期計画の実施状況と評価」を新設**し、**「介護保険事業等の見込み」を独立章（第6章・9節）に立て直した。**資料編に4項目（成果指標の定義／年次評価の様式／施策の見直しの基準／主な参照資料）を加え、5章構成から6章構成に組み替えた。**9月29日に書体を游ゴシック10.5pt（表8.5pt・出典8.5pt、見出しH1 15pt・H2 12.5pt・H3 11pt、上下余白2.0cm・左右1.9cm）に改め、成果品全体でそろえた。**対比は check_ono_taihi.py が毎回再計算するため、素案を直せば対比表も追従する。**10月4日に3項目を解消した。****①第6章10「中長期の見通し（令和22年・令和32年）」を新設**（総給付費は令和22年で＋12.8％にとどまるが、第1号被保険者1人当たりでは＋28.7％、令和32年では＋39.5％になる）。**②第1章2に、国が第10期に求める5点と、確認すべき制度改正5件の表を加えた**（公布・公表が確認できた事項に限り、先取りはしていない）。**③資料編12「図表番号一覧」を新設し、すべての表に通し番号を振った**（表題は見出しから機械的に作るため、見出しを変えても題が古くならない）</t>
+          <t>**9月29日に、他団体の第10期計画の見出し129件を機械的に抽出し、小野町の素案と44項目で対比した（03_計画素案）。****○18件・△11件・×14件・該当なし1件で、うち16件を素案に反映済みである。**第1章に3節（計画策定の視点／日常生活圏域の設定／計画の進行管理・推進体制）、**第3章「第9期計画の実施状況と評価」を新設**し、**「介護保険事業等の見込み」を独立章（第6章・9節）に立て直した。**資料編に4項目（成果指標の定義／年次評価の様式／施策の見直しの基準／主な参照資料）を加え、5章構成から6章構成に組み替えた。**9月29日に書体を游ゴシック10.5pt（表8.5pt・出典8.5pt、見出しH1 15pt・H2 12.5pt・H3 11pt、上下余白2.0cm・左右1.9cm）に改め、成果品全体でそろえた。**対比は check_ono_taihi.py が毎回再計算するため、素案を直せば対比表も追従する。**10月5日に、第5章の各施策に【関連データ】の表を加えた（12施策・74行）。****他団体が置いている5項目のうち、本町に無かった「関連データ」である。****値は一次資料の台帳（原本と照合済みの286件）から引く作りにしたため、本文と表がずれない。台帳に無いキーを書くと生成が止まる。**これで対比は○22／△9／×12となった。**10月4日に3項目を解消した。****①第6章10「中長期の見通し（令和22年・令和32年）」を新設**（総給付費は令和22年で＋12.8％にとどまるが、第1号被保険者1人当たりでは＋28.7％、令和32年では＋39.5％になる）。**②第1章2に、国が第10期に求める5点と、確認すべき制度改正5件の表を加えた**（公布・公表が確認できた事項に限り、先取りはしていない）。**③資料編12「図表番号一覧」を新設し、すべての表に通し番号を振った**（表題は見出しから機械的に作るため、見出しを変えても題が古くならない）</t>
         </is>
       </c>
       <c r="O55" s="19" t="inlineStr">

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20261005.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20261005.xlsx
@@ -21,8 +21,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_進捗の乖離" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_WBS'!$A$1:$O$77</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'11_進捗の乖離'!$A$1:$M$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_WBS'!$A$1:$O$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'11_進捗の乖離'!$A$1:$M$78</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.5514041450777202</v>
+        <v>0.5492474226804124</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.7018134715025908</v>
+        <v>0.7033505154639176</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -722,13 +722,13 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.1504093264248705</v>
+        <v>0.1541030927835052</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>おおむね予定どおり 46件／前倒し 22件／遅れ 4件／期限超過（2か月） 2件／期限超過（1か月） 2件</t>
+          <t>おおむね予定どおり 46件／前倒し 23件／遅れ 4件／期限超過（2か月） 2件／期限超過（1か月） 2件</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="D66" s="13" t="inlineStr">
         <is>
-          <t>令和9年2月下旬の校了から逆算し、12月までに印刷業者を押さえる</t>
+          <t>令和9年2月下旬の校了から逆算すると発注は2月中旬まで待てるが、年度末の印刷の集中を見て1月中に押さえる</t>
         </is>
       </c>
       <c r="E66" s="13" t="n"/>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="D83" s="13" t="inlineStr">
         <is>
-          <t>**12月までに発注しないと2月の校了に間に合わない**</t>
+          <t>**年度末は印刷が集中するため1月中に業者を押さえる**</t>
         </is>
       </c>
       <c r="E83" s="13" t="n"/>
@@ -2858,11 +2858,12 @@
         <is>
           <t>10-2 レイアウト・組版
 10-3 校正（初校・再校・校了）
-10-6 印刷・製本</t>
+10-6 印刷・製本
+10-9 印刷の発注準備</t>
         </is>
       </c>
       <c r="E23" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" s="21" t="inlineStr">
         <is>
@@ -2890,11 +2891,12 @@
         <is>
           <t>10-4 概要版の構成案
 10-5 概要版の作成
-10-6 印刷・製本</t>
+10-6 印刷・製本
+10-9 印刷の発注準備</t>
         </is>
       </c>
       <c r="E24" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F24" s="21" t="inlineStr">
         <is>
@@ -3159,31 +3161,31 @@
         </is>
       </c>
       <c r="C2" s="20">
-        <f>COUNTIF('01_WBS'!$E$2:$E$77,$A2)</f>
+        <f>COUNTIF('01_WBS'!$E$2:$E$78,$A2)</f>
         <v/>
       </c>
       <c r="D2" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A2,'01_WBS'!$K$2:$K$77,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A2,'01_WBS'!$K$2:$K$78,"完了")</f>
         <v/>
       </c>
       <c r="E2" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A2,'01_WBS'!$K$2:$K$77,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A2,'01_WBS'!$K$2:$K$78,"進行中")</f>
         <v/>
       </c>
       <c r="F2" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A2,'01_WBS'!$K$2:$K$77,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A2,'01_WBS'!$K$2:$K$78,"要対応")</f>
         <v/>
       </c>
       <c r="G2" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A2,'01_WBS'!$K$2:$K$77,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A2,'01_WBS'!$K$2:$K$78,"データ待ち")</f>
         <v/>
       </c>
       <c r="H2" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A2,'01_WBS'!$K$2:$K$77,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A2,'01_WBS'!$K$2:$K$78,"未着手")</f>
         <v/>
       </c>
       <c r="I2" s="28">
-        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A2)*'01_WBS'!$M$2:$M$77)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A2)*'01_WBS'!$L$2:$L$77*'01_WBS'!$M$2:$M$77)/SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A2)*'01_WBS'!$M$2:$M$77)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A2)*'01_WBS'!$M$2:$M$78)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A2)*'01_WBS'!$L$2:$L$78*'01_WBS'!$M$2:$M$78)/SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A2)*'01_WBS'!$M$2:$M$78)/100)</f>
         <v/>
       </c>
       <c r="J2" s="19" t="inlineStr">
@@ -3204,31 +3206,31 @@
         </is>
       </c>
       <c r="C3" s="20">
-        <f>COUNTIF('01_WBS'!$E$2:$E$77,$A3)</f>
+        <f>COUNTIF('01_WBS'!$E$2:$E$78,$A3)</f>
         <v/>
       </c>
       <c r="D3" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A3,'01_WBS'!$K$2:$K$77,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A3,'01_WBS'!$K$2:$K$78,"完了")</f>
         <v/>
       </c>
       <c r="E3" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A3,'01_WBS'!$K$2:$K$77,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A3,'01_WBS'!$K$2:$K$78,"進行中")</f>
         <v/>
       </c>
       <c r="F3" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A3,'01_WBS'!$K$2:$K$77,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A3,'01_WBS'!$K$2:$K$78,"要対応")</f>
         <v/>
       </c>
       <c r="G3" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A3,'01_WBS'!$K$2:$K$77,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A3,'01_WBS'!$K$2:$K$78,"データ待ち")</f>
         <v/>
       </c>
       <c r="H3" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A3,'01_WBS'!$K$2:$K$77,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A3,'01_WBS'!$K$2:$K$78,"未着手")</f>
         <v/>
       </c>
       <c r="I3" s="28">
-        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A3)*'01_WBS'!$M$2:$M$77)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A3)*'01_WBS'!$L$2:$L$77*'01_WBS'!$M$2:$M$77)/SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A3)*'01_WBS'!$M$2:$M$77)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A3)*'01_WBS'!$M$2:$M$78)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A3)*'01_WBS'!$L$2:$L$78*'01_WBS'!$M$2:$M$78)/SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A3)*'01_WBS'!$M$2:$M$78)/100)</f>
         <v/>
       </c>
       <c r="J3" s="19" t="inlineStr">
@@ -3249,31 +3251,31 @@
         </is>
       </c>
       <c r="C4" s="20">
-        <f>COUNTIF('01_WBS'!$E$2:$E$77,$A4)</f>
+        <f>COUNTIF('01_WBS'!$E$2:$E$78,$A4)</f>
         <v/>
       </c>
       <c r="D4" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A4,'01_WBS'!$K$2:$K$77,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A4,'01_WBS'!$K$2:$K$78,"完了")</f>
         <v/>
       </c>
       <c r="E4" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A4,'01_WBS'!$K$2:$K$77,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A4,'01_WBS'!$K$2:$K$78,"進行中")</f>
         <v/>
       </c>
       <c r="F4" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A4,'01_WBS'!$K$2:$K$77,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A4,'01_WBS'!$K$2:$K$78,"要対応")</f>
         <v/>
       </c>
       <c r="G4" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A4,'01_WBS'!$K$2:$K$77,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A4,'01_WBS'!$K$2:$K$78,"データ待ち")</f>
         <v/>
       </c>
       <c r="H4" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A4,'01_WBS'!$K$2:$K$77,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A4,'01_WBS'!$K$2:$K$78,"未着手")</f>
         <v/>
       </c>
       <c r="I4" s="28">
-        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A4)*'01_WBS'!$M$2:$M$77)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A4)*'01_WBS'!$L$2:$L$77*'01_WBS'!$M$2:$M$77)/SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A4)*'01_WBS'!$M$2:$M$77)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A4)*'01_WBS'!$M$2:$M$78)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A4)*'01_WBS'!$L$2:$L$78*'01_WBS'!$M$2:$M$78)/SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A4)*'01_WBS'!$M$2:$M$78)/100)</f>
         <v/>
       </c>
       <c r="J4" s="19" t="inlineStr">
@@ -3294,31 +3296,31 @@
         </is>
       </c>
       <c r="C5" s="20">
-        <f>COUNTIF('01_WBS'!$E$2:$E$77,$A5)</f>
+        <f>COUNTIF('01_WBS'!$E$2:$E$78,$A5)</f>
         <v/>
       </c>
       <c r="D5" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A5,'01_WBS'!$K$2:$K$77,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A5,'01_WBS'!$K$2:$K$78,"完了")</f>
         <v/>
       </c>
       <c r="E5" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A5,'01_WBS'!$K$2:$K$77,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A5,'01_WBS'!$K$2:$K$78,"進行中")</f>
         <v/>
       </c>
       <c r="F5" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A5,'01_WBS'!$K$2:$K$77,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A5,'01_WBS'!$K$2:$K$78,"要対応")</f>
         <v/>
       </c>
       <c r="G5" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A5,'01_WBS'!$K$2:$K$77,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A5,'01_WBS'!$K$2:$K$78,"データ待ち")</f>
         <v/>
       </c>
       <c r="H5" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A5,'01_WBS'!$K$2:$K$77,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A5,'01_WBS'!$K$2:$K$78,"未着手")</f>
         <v/>
       </c>
       <c r="I5" s="28">
-        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A5)*'01_WBS'!$M$2:$M$77)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A5)*'01_WBS'!$L$2:$L$77*'01_WBS'!$M$2:$M$77)/SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A5)*'01_WBS'!$M$2:$M$77)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A5)*'01_WBS'!$M$2:$M$78)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A5)*'01_WBS'!$L$2:$L$78*'01_WBS'!$M$2:$M$78)/SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A5)*'01_WBS'!$M$2:$M$78)/100)</f>
         <v/>
       </c>
       <c r="J5" s="19" t="inlineStr">
@@ -3339,31 +3341,31 @@
         </is>
       </c>
       <c r="C6" s="20">
-        <f>COUNTIF('01_WBS'!$E$2:$E$77,$A6)</f>
+        <f>COUNTIF('01_WBS'!$E$2:$E$78,$A6)</f>
         <v/>
       </c>
       <c r="D6" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A6,'01_WBS'!$K$2:$K$77,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A6,'01_WBS'!$K$2:$K$78,"完了")</f>
         <v/>
       </c>
       <c r="E6" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A6,'01_WBS'!$K$2:$K$77,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A6,'01_WBS'!$K$2:$K$78,"進行中")</f>
         <v/>
       </c>
       <c r="F6" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A6,'01_WBS'!$K$2:$K$77,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A6,'01_WBS'!$K$2:$K$78,"要対応")</f>
         <v/>
       </c>
       <c r="G6" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A6,'01_WBS'!$K$2:$K$77,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A6,'01_WBS'!$K$2:$K$78,"データ待ち")</f>
         <v/>
       </c>
       <c r="H6" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A6,'01_WBS'!$K$2:$K$77,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A6,'01_WBS'!$K$2:$K$78,"未着手")</f>
         <v/>
       </c>
       <c r="I6" s="28">
-        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A6)*'01_WBS'!$M$2:$M$77)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A6)*'01_WBS'!$L$2:$L$77*'01_WBS'!$M$2:$M$77)/SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A6)*'01_WBS'!$M$2:$M$77)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A6)*'01_WBS'!$M$2:$M$78)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A6)*'01_WBS'!$L$2:$L$78*'01_WBS'!$M$2:$M$78)/SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A6)*'01_WBS'!$M$2:$M$78)/100)</f>
         <v/>
       </c>
       <c r="J6" s="19" t="inlineStr">
@@ -3384,31 +3386,31 @@
         </is>
       </c>
       <c r="C7" s="20">
-        <f>COUNTIF('01_WBS'!$E$2:$E$77,$A7)</f>
+        <f>COUNTIF('01_WBS'!$E$2:$E$78,$A7)</f>
         <v/>
       </c>
       <c r="D7" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A7,'01_WBS'!$K$2:$K$77,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A7,'01_WBS'!$K$2:$K$78,"完了")</f>
         <v/>
       </c>
       <c r="E7" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A7,'01_WBS'!$K$2:$K$77,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A7,'01_WBS'!$K$2:$K$78,"進行中")</f>
         <v/>
       </c>
       <c r="F7" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A7,'01_WBS'!$K$2:$K$77,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A7,'01_WBS'!$K$2:$K$78,"要対応")</f>
         <v/>
       </c>
       <c r="G7" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A7,'01_WBS'!$K$2:$K$77,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A7,'01_WBS'!$K$2:$K$78,"データ待ち")</f>
         <v/>
       </c>
       <c r="H7" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A7,'01_WBS'!$K$2:$K$77,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A7,'01_WBS'!$K$2:$K$78,"未着手")</f>
         <v/>
       </c>
       <c r="I7" s="28">
-        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A7)*'01_WBS'!$M$2:$M$77)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A7)*'01_WBS'!$L$2:$L$77*'01_WBS'!$M$2:$M$77)/SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A7)*'01_WBS'!$M$2:$M$77)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A7)*'01_WBS'!$M$2:$M$78)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A7)*'01_WBS'!$L$2:$L$78*'01_WBS'!$M$2:$M$78)/SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A7)*'01_WBS'!$M$2:$M$78)/100)</f>
         <v/>
       </c>
       <c r="J7" s="19" t="inlineStr">
@@ -3429,31 +3431,31 @@
         </is>
       </c>
       <c r="C8" s="20">
-        <f>COUNTIF('01_WBS'!$E$2:$E$77,$A8)</f>
+        <f>COUNTIF('01_WBS'!$E$2:$E$78,$A8)</f>
         <v/>
       </c>
       <c r="D8" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A8,'01_WBS'!$K$2:$K$77,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A8,'01_WBS'!$K$2:$K$78,"完了")</f>
         <v/>
       </c>
       <c r="E8" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A8,'01_WBS'!$K$2:$K$77,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A8,'01_WBS'!$K$2:$K$78,"進行中")</f>
         <v/>
       </c>
       <c r="F8" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A8,'01_WBS'!$K$2:$K$77,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A8,'01_WBS'!$K$2:$K$78,"要対応")</f>
         <v/>
       </c>
       <c r="G8" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A8,'01_WBS'!$K$2:$K$77,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A8,'01_WBS'!$K$2:$K$78,"データ待ち")</f>
         <v/>
       </c>
       <c r="H8" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A8,'01_WBS'!$K$2:$K$77,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A8,'01_WBS'!$K$2:$K$78,"未着手")</f>
         <v/>
       </c>
       <c r="I8" s="28">
-        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A8)*'01_WBS'!$M$2:$M$77)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A8)*'01_WBS'!$L$2:$L$77*'01_WBS'!$M$2:$M$77)/SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A8)*'01_WBS'!$M$2:$M$77)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A8)*'01_WBS'!$M$2:$M$78)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A8)*'01_WBS'!$L$2:$L$78*'01_WBS'!$M$2:$M$78)/SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A8)*'01_WBS'!$M$2:$M$78)/100)</f>
         <v/>
       </c>
       <c r="J8" s="19" t="inlineStr">
@@ -3474,31 +3476,31 @@
         </is>
       </c>
       <c r="C9" s="20">
-        <f>COUNTIF('01_WBS'!$E$2:$E$77,$A9)</f>
+        <f>COUNTIF('01_WBS'!$E$2:$E$78,$A9)</f>
         <v/>
       </c>
       <c r="D9" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A9,'01_WBS'!$K$2:$K$77,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A9,'01_WBS'!$K$2:$K$78,"完了")</f>
         <v/>
       </c>
       <c r="E9" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A9,'01_WBS'!$K$2:$K$77,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A9,'01_WBS'!$K$2:$K$78,"進行中")</f>
         <v/>
       </c>
       <c r="F9" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A9,'01_WBS'!$K$2:$K$77,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A9,'01_WBS'!$K$2:$K$78,"要対応")</f>
         <v/>
       </c>
       <c r="G9" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A9,'01_WBS'!$K$2:$K$77,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A9,'01_WBS'!$K$2:$K$78,"データ待ち")</f>
         <v/>
       </c>
       <c r="H9" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A9,'01_WBS'!$K$2:$K$77,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A9,'01_WBS'!$K$2:$K$78,"未着手")</f>
         <v/>
       </c>
       <c r="I9" s="28">
-        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A9)*'01_WBS'!$M$2:$M$77)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A9)*'01_WBS'!$L$2:$L$77*'01_WBS'!$M$2:$M$77)/SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A9)*'01_WBS'!$M$2:$M$77)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A9)*'01_WBS'!$M$2:$M$78)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A9)*'01_WBS'!$L$2:$L$78*'01_WBS'!$M$2:$M$78)/SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A9)*'01_WBS'!$M$2:$M$78)/100)</f>
         <v/>
       </c>
       <c r="J9" s="19" t="inlineStr">
@@ -3519,31 +3521,31 @@
         </is>
       </c>
       <c r="C10" s="20">
-        <f>COUNTIF('01_WBS'!$E$2:$E$77,$A10)</f>
+        <f>COUNTIF('01_WBS'!$E$2:$E$78,$A10)</f>
         <v/>
       </c>
       <c r="D10" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A10,'01_WBS'!$K$2:$K$77,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A10,'01_WBS'!$K$2:$K$78,"完了")</f>
         <v/>
       </c>
       <c r="E10" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A10,'01_WBS'!$K$2:$K$77,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A10,'01_WBS'!$K$2:$K$78,"進行中")</f>
         <v/>
       </c>
       <c r="F10" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A10,'01_WBS'!$K$2:$K$77,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A10,'01_WBS'!$K$2:$K$78,"要対応")</f>
         <v/>
       </c>
       <c r="G10" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A10,'01_WBS'!$K$2:$K$77,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A10,'01_WBS'!$K$2:$K$78,"データ待ち")</f>
         <v/>
       </c>
       <c r="H10" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A10,'01_WBS'!$K$2:$K$77,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A10,'01_WBS'!$K$2:$K$78,"未着手")</f>
         <v/>
       </c>
       <c r="I10" s="28">
-        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A10)*'01_WBS'!$M$2:$M$77)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A10)*'01_WBS'!$L$2:$L$77*'01_WBS'!$M$2:$M$77)/SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A10)*'01_WBS'!$M$2:$M$77)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A10)*'01_WBS'!$M$2:$M$78)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A10)*'01_WBS'!$L$2:$L$78*'01_WBS'!$M$2:$M$78)/SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A10)*'01_WBS'!$M$2:$M$78)/100)</f>
         <v/>
       </c>
       <c r="J10" s="19" t="inlineStr">
@@ -3564,31 +3566,31 @@
         </is>
       </c>
       <c r="C11" s="20">
-        <f>COUNTIF('01_WBS'!$E$2:$E$77,$A11)</f>
+        <f>COUNTIF('01_WBS'!$E$2:$E$78,$A11)</f>
         <v/>
       </c>
       <c r="D11" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A11,'01_WBS'!$K$2:$K$77,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A11,'01_WBS'!$K$2:$K$78,"完了")</f>
         <v/>
       </c>
       <c r="E11" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A11,'01_WBS'!$K$2:$K$77,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A11,'01_WBS'!$K$2:$K$78,"進行中")</f>
         <v/>
       </c>
       <c r="F11" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A11,'01_WBS'!$K$2:$K$77,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A11,'01_WBS'!$K$2:$K$78,"要対応")</f>
         <v/>
       </c>
       <c r="G11" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A11,'01_WBS'!$K$2:$K$77,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A11,'01_WBS'!$K$2:$K$78,"データ待ち")</f>
         <v/>
       </c>
       <c r="H11" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A11,'01_WBS'!$K$2:$K$77,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A11,'01_WBS'!$K$2:$K$78,"未着手")</f>
         <v/>
       </c>
       <c r="I11" s="28">
-        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A11)*'01_WBS'!$M$2:$M$77)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A11)*'01_WBS'!$L$2:$L$77*'01_WBS'!$M$2:$M$77)/SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A11)*'01_WBS'!$M$2:$M$77)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A11)*'01_WBS'!$M$2:$M$78)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A11)*'01_WBS'!$L$2:$L$78*'01_WBS'!$M$2:$M$78)/SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A11)*'01_WBS'!$M$2:$M$78)/100)</f>
         <v/>
       </c>
       <c r="J11" s="19" t="inlineStr">
@@ -3609,31 +3611,31 @@
         </is>
       </c>
       <c r="C12" s="20">
-        <f>COUNTIF('01_WBS'!$E$2:$E$77,$A12)</f>
+        <f>COUNTIF('01_WBS'!$E$2:$E$78,$A12)</f>
         <v/>
       </c>
       <c r="D12" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A12,'01_WBS'!$K$2:$K$77,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A12,'01_WBS'!$K$2:$K$78,"完了")</f>
         <v/>
       </c>
       <c r="E12" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A12,'01_WBS'!$K$2:$K$77,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A12,'01_WBS'!$K$2:$K$78,"進行中")</f>
         <v/>
       </c>
       <c r="F12" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A12,'01_WBS'!$K$2:$K$77,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A12,'01_WBS'!$K$2:$K$78,"要対応")</f>
         <v/>
       </c>
       <c r="G12" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A12,'01_WBS'!$K$2:$K$77,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A12,'01_WBS'!$K$2:$K$78,"データ待ち")</f>
         <v/>
       </c>
       <c r="H12" s="20">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$77,$A12,'01_WBS'!$K$2:$K$77,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$78,$A12,'01_WBS'!$K$2:$K$78,"未着手")</f>
         <v/>
       </c>
       <c r="I12" s="28">
-        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A12)*'01_WBS'!$M$2:$M$77)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A12)*'01_WBS'!$L$2:$L$77*'01_WBS'!$M$2:$M$77)/SUMPRODUCT(('01_WBS'!$E$2:$E$77=$A12)*'01_WBS'!$M$2:$M$77)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A12)*'01_WBS'!$M$2:$M$78)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A12)*'01_WBS'!$L$2:$L$78*'01_WBS'!$M$2:$M$78)/SUMPRODUCT(('01_WBS'!$E$2:$E$78=$A12)*'01_WBS'!$M$2:$M$78)/100)</f>
         <v/>
       </c>
       <c r="J12" s="19" t="inlineStr">
@@ -3674,7 +3676,7 @@
         <v/>
       </c>
       <c r="I13" s="31">
-        <f>IF(SUM('01_WBS'!$M$2:$M$77)=0,0,SUMPRODUCT('01_WBS'!$L$2:$L$77,'01_WBS'!$M$2:$M$77)/SUM('01_WBS'!$M$2:$M$77)/100)</f>
+        <f>IF(SUM('01_WBS'!$M$2:$M$78)=0,0,SUMPRODUCT('01_WBS'!$L$2:$L$78,'01_WBS'!$M$2:$M$78)/SUM('01_WBS'!$M$2:$M$78)/100)</f>
         <v/>
       </c>
       <c r="J13" s="19" t="inlineStr"/>
@@ -3711,7 +3713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8224,127 +8226,186 @@
     <row r="77">
       <c r="A77" s="19" t="inlineStr">
         <is>
+          <t>P10 完成・納品</t>
+        </is>
+      </c>
+      <c r="B77" s="20" t="inlineStr">
+        <is>
+          <t>10-9</t>
+        </is>
+      </c>
+      <c r="C77" s="19" t="inlineStr">
+        <is>
+          <t>印刷の発注準備</t>
+        </is>
+      </c>
+      <c r="D77" s="20" t="inlineStr">
+        <is>
+          <t>受託者</t>
+        </is>
+      </c>
+      <c r="E77" s="20" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="F77" s="20" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G77" s="21" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="H77" s="32" t="n">
+        <v>100</v>
+      </c>
+      <c r="I77" s="32" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="J77" s="32" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="K77" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" s="33" t="inlineStr">
+        <is>
+          <t>前倒し</t>
+        </is>
+      </c>
+      <c r="M77" s="19" t="inlineStr">
+        <is>
+          <t>町による用紙・校正の条件の決定</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="19" t="inlineStr">
+        <is>
           <t>P7 推計・算定</t>
         </is>
       </c>
-      <c r="B77" s="20" t="inlineStr">
+      <c r="B78" s="20" t="inlineStr">
         <is>
           <t>7-6</t>
         </is>
       </c>
-      <c r="C77" s="19" t="inlineStr">
+      <c r="C78" s="19" t="inlineStr">
         <is>
           <t>保険料のケース別算定</t>
         </is>
       </c>
-      <c r="D77" s="20" t="inlineStr">
+      <c r="D78" s="20" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="E77" s="20" t="inlineStr">
+      <c r="E78" s="20" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="F77" s="20" t="inlineStr">
+      <c r="F78" s="20" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="G77" s="23" t="inlineStr">
+      <c r="G78" s="23" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="H77" s="32" t="n">
+      <c r="H78" s="32" t="n">
         <v>95</v>
       </c>
-      <c r="I77" s="32" t="n">
+      <c r="I78" s="32" t="n">
         <v>6.7</v>
       </c>
-      <c r="J77" s="32" t="n">
+      <c r="J78" s="32" t="n">
         <v>88.3</v>
       </c>
-      <c r="K77" s="20" t="n">
+      <c r="K78" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="L77" s="33" t="inlineStr">
+      <c r="L78" s="33" t="inlineStr">
         <is>
           <t>前倒し</t>
         </is>
       </c>
-      <c r="M77" s="19" t="inlineStr">
+      <c r="M78" s="19" t="inlineStr">
         <is>
           <t>**一般介護予防事業費と包括的支援事業・任意事業費の事業別内訳、令和7年度の決算額（年報が未入力）、調整交付金見込額、第10期の第1号被保険者負担割合。あわせて、第9期が見込んだ基金取崩35,000千円に対し基金保有額が12,000千円しかない点の確認が要る（しかも年報の残高の系列に矛盾がある）**</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="34" t="inlineStr">
-        <is>
-          <t>加重の実績進捗率 70.2％　対　予定進捗率 55.1％　乖離 +15.0ポイント</t>
-        </is>
-      </c>
-    </row>
     <row r="80">
-      <c r="A80" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　期限超過 4件</t>
+      <c r="A80" s="34" t="inlineStr">
+        <is>
+          <t>加重の実績進捗率 70.3％　対　予定進捗率 54.9％　乖離 +15.4ポイント</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">　遅れ 4件</t>
+          <t xml:space="preserve">　期限超過 4件</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">　おおむね予定どおり 46件</t>
+          <t xml:space="preserve">　遅れ 4件</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">　前倒し 22件</t>
+          <t xml:space="preserve">　おおむね予定どおり 46件</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="36" t="inlineStr">
-        <is>
-          <t>※ 予定進捗率＝予定開始の月初から予定完了の月末までを直線で見たとき、基準日に何％進んでいるはずかの値です。</t>
+      <c r="A84" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　前倒し 23件</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="36" t="inlineStr">
         <is>
-          <t>※ 判定は実績と予定の差が±10ポイント以内なら「おおむね予定どおり」としています。月単位の予定を日割りした誤差の幅です。</t>
+          <t>※ 予定進捗率＝予定開始の月初から予定完了の月末までを直線で見たとき、基準日に何％進んでいるはずかの値です。</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="36" t="inlineStr">
         <is>
-          <t>※ 予定完了の月を過ぎてなお完了していないものを「期限超過」としています。</t>
+          <t>※ 判定は実績と予定の差が±10ポイント以内なら「おおむね予定どおり」としています。月単位の予定を日割りした誤差の幅です。</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="36" t="inlineStr">
         <is>
+          <t>※ 予定完了の月を過ぎてなお完了していないものを「期限超過」としています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="36" t="inlineStr">
+        <is>
           <t>※ 加重は工数の目安（重み1〜5）です。製本1件の遅れと見込量推計1件の遅れを同じ重さにしないためです。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M77"/>
+  <autoFilter ref="A1:M78"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8355,7 +8416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W77"/>
+  <dimension ref="A1:W78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11695,7 +11756,7 @@
       </c>
       <c r="Q41" s="20" t="inlineStr">
         <is>
-          <t>**9月24日に、他町村の手引きの14段階で自己点検した（見込量算定の手引き適合点検・04_算定・見込量）。**済んでいなかった6段階（内的整合・季節性・施策反映・趨勢外の要因・記載事項・自己点検）を埋めた。**新たに分かったことが3つある。**①**単価は報酬改定のない年でも年率＋1.09％伸びており、改定のあった令和6年度の＋1.25％と差がない。**当方は単価を令和7年度で固定しているため、実績の趨勢（年率＋1.13％）で置くと標準給付費が3.43％・保険料が月額211円上がる。固定は過小側の置き方である。②**季節性は、居宅・地域密着型が年度で向きが逆になり再現しない。**施設（冬季が高い）と受給者計（冬季が低い）は再現するが差は2％前後で向きが逆であり相殺される。基準年度が完結年度のため補正は不要。③**施策反映は、当方の式で変数になっているのが第1号被保険者数だけであり、成果指標40件のうち目標値が確定しているものが0件であるため、現時点で反映できるものがない。**歯止めを先に定めた。**自己点検12項目を算定に組み込み、変異試験3件すべてで止まることを確かめた。**</t>
+          <t>**9月24日に、他町村の手引きの14段階で自己点検した（見込量算定の手引き適合点検・04_算定・見込量）。**済んでいなかった6段階（内的整合・季節性・施策反映・趨勢外の要因・記載事項・自己点検）を埋めた。**新たに分かったことが3つある。**①**単価は報酬改定のない年でも年率＋1.09％伸びており、改定のあった令和6年度の＋1.25％と差がない。**当方は単価を令和7年度で固定しているため、実績の趨勢（年率＋1.13％）で置くと標準給付費が3.43％・保険料が月額195円上がる。固定は過小側の置き方である。②**季節性は、居宅・地域密着型が年度で向きが逆になり再現しない。**施設（冬季が高い）と受給者計（冬季が低い）は再現するが差は2％前後で向きが逆であり相殺される。基準年度が完結年度のため補正は不要。③**施策反映は、当方の式で変数になっているのが第1号被保険者数だけであり、成果指標40件のうち目標値が確定しているものが0件であるため、現時点で反映できるものがない。**歯止めを先に定めた。**自己点検12項目を算定に組み込み、変異試験3件すべてで止まることを確かめた。**</t>
         </is>
       </c>
       <c r="R41" s="20" t="inlineStr">
@@ -11725,7 +11786,7 @@
       </c>
       <c r="W41" s="20" t="inlineStr">
         <is>
-          <t>**報酬改定率（令和9年度）の確定。**あわせて、訪問介護の基準期間（3年平均だと令和9年度の見込件数が令和7年度実績の1.27倍。令和7年度単年なら月額▲47円）を協議会にお諮りする。**必要利用定員総数は、認知症対応型共同生活介護の定員が令和4年度71人から令和6年度98人へ増えた経緯と町外の方の利用割合を町に確認したうえで確定する。****あわせて、単価を令和7年度で固定していることを協議会にお諮りする（実績の趨勢で置くと月額＋211円）**</t>
+          <t>**報酬改定率（令和9年度）の確定。**あわせて、訪問介護の基準期間（3年平均だと令和9年度の見込件数が令和7年度実績の1.27倍。令和7年度単年なら月額▲47円）を協議会にお諮りする。**必要利用定員総数は、認知症対応型共同生活介護の定員が令和4年度71人から令和6年度98人へ増えた経緯と町外の方の利用割合を町に確認したうえで確定する。****あわせて、単価を令和7年度で固定していることを協議会にお諮りする（実績の趨勢で置くと月額＋195円）**</t>
         </is>
       </c>
     </row>
@@ -13991,7 +14052,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>**逆算表を作成済み。12月までに印刷業者を押さえる必要がある**</t>
+          <t>**発注仕様書と見積依頼の様式を作成済み（令和8年10月6日）。年度末の印刷の集中を見て1月中に業者を押さえる**</t>
         </is>
       </c>
       <c r="O69" s="19" t="inlineStr">
@@ -14173,37 +14234,38 @@
     <row r="72">
       <c r="A72" s="19" t="inlineStr">
         <is>
-          <t>P11 品質・進捗管理</t>
+          <t>P10 完成・納品</t>
         </is>
       </c>
       <c r="B72" s="20" t="inlineStr">
         <is>
-          <t>11-1</t>
+          <t>10-9</t>
         </is>
       </c>
       <c r="C72" s="19" t="inlineStr">
         <is>
-          <t>一次資料との全件突合</t>
+          <t>印刷の発注準備</t>
         </is>
       </c>
       <c r="D72" s="19" t="inlineStr">
         <is>
-          <t>成果品に載せた数値を、町から受領した原本（年報・月報・調査結果報告書・交付金の集計表）と1件ずつ突き合わせる</t>
+          <t>発注仕様書（用紙・綴じ・校正の回数）と見積依頼の様式・比較表</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr">
         <is>
-          <t>B10 業務管理・計画の基本的な考え方</t>
+          <t>B9 成果品の納品</t>
         </is>
       </c>
       <c r="F72" s="20" t="inlineStr">
         <is>
-          <t>仕様書全般</t>
+          <t>仕様書4 成果品⑤・仕様書4 成果品⑥</t>
         </is>
       </c>
       <c r="G72" s="19" t="inlineStr">
         <is>
-          <t>【全般】委託仕様書及び公告の全体（成果品要件・工程・作業分担の確認）</t>
+          <t>【成果品⑤】（5）小野町高齢者保健福祉計画・第10期介護保険事業計画　※データ（CD-R）1部、計画書印刷50部＜仕様＞A4版、4色刷り、80頁程度
+【成果品⑥】（6）小野町高齢者保健福祉計画・第10期介護保険事業計画概要版　※データ（CD-R）1部、概要版印刷50部＜仕様＞A4版、4色刷り、8頁</t>
         </is>
       </c>
       <c r="H72" s="20" t="inlineStr">
@@ -14213,33 +14275,33 @@
       </c>
       <c r="I72" s="20" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="J72" s="20" t="inlineStr">
         <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="K72" s="23" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K72" s="21" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L72" s="22" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="M72" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>**check_ono_ichiji.py が286件を毎回照合し、NGがあれば止まる。現在NGは0件である。****9月29日に調査結果報告書の原本を取り込み、配布・回収、リスク該当率10項目、通いの場、外出、認知症（問35・問36）、在宅介護実態調査の属性・利用状況・未利用理由・介護者、問9（仕事と介護の両立の支援12項目）を全件突合した。****これにより、報告書そのものの食い違い3件を特定した**（①回収数319に対し集計基数366、②通いの場が本文67.2％・図76.2％、③p.84のまとめで項目名が重複）。**あわせて、当方の成果品にあった項目名の取り違えを正した。**問36の54.1％は「相談窓口の充実」ではなく**「地域での見守りや声掛け」**であり、選択肢に「相談窓口の充実」は存在しない（素案・協議会資料・調査結果の分析・交付金の4点を訂正）。**点検の結果はOK 280件・NG 0件・説明のつく相違4件・一次資料が手元にないもの2件である。**相違はいずれも理由とともに記録している</t>
+          <t>**印刷の発注仕様書・見積依頼書と内訳の様式（10_納品・印刷、令和8年10月6日）。仕様書に定めのない8条件に推奨を置き、見積の内訳13工程を固定した。発注の逆算で、校了に間に合わせるだけなら2月中旬まで待てることが分かった**</t>
         </is>
       </c>
       <c r="O72" s="19" t="inlineStr">
         <is>
-          <t>**町データが届くたびに突合対象が増える。とくに成果指標の現状値17項目と令和7年度決算が入ると、素案・算定シート・協議会資料の3系統を同時に照合する必要がある**</t>
+          <t>町による用紙・校正の条件の決定</t>
         </is>
       </c>
       <c r="P72" s="24" t="n"/>
@@ -14259,17 +14321,17 @@
       </c>
       <c r="B73" s="20" t="inlineStr">
         <is>
-          <t>11-2</t>
+          <t>11-1</t>
         </is>
       </c>
       <c r="C73" s="19" t="inlineStr">
         <is>
-          <t>図表データ管理台帳の整備と運用</t>
+          <t>一次資料との全件突合</t>
         </is>
       </c>
       <c r="D73" s="19" t="inlineStr">
         <is>
-          <t>成果品に載せる図表の出所・算定根拠・差し込み先を1枚で追えるようにする</t>
+          <t>成果品に載せた数値を、町から受領した原本（年報・月報・調査結果報告書・交付金の集計表）と1件ずつ突き合わせる</t>
         </is>
       </c>
       <c r="E73" s="19" t="inlineStr">
@@ -14311,16 +14373,16 @@
         <v>85</v>
       </c>
       <c r="M73" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>**9月30日に図表データ管理台帳（25シート）を新設した（22_図表管理）。**図22点の差し込み先、交付金の評価指標との紐付け11件、成果品9件との対応、足りない図6件を一覧にしている。**台帳の数値は ono_figs.py の共通出口から自動で控える仕組みにした**（matplotlib の描画オブジェクトから系列名と数値を読み取り、_ledger.json に書き出す）。手で転記しないため、図と台帳がずれない。**小野町は図を一次資料から毎回計算する作りであるため、台帳は正本ではなく控えである旨を00シートに明記した**</t>
+          <t>**check_ono_ichiji.py が286件を毎回照合し、NGがあれば止まる。現在NGは0件である。****9月29日に調査結果報告書の原本を取り込み、配布・回収、リスク該当率10項目、通いの場、外出、認知症（問35・問36）、在宅介護実態調査の属性・利用状況・未利用理由・介護者、問9（仕事と介護の両立の支援12項目）を全件突合した。****これにより、報告書そのものの食い違い3件を特定した**（①回収数319に対し集計基数366、②通いの場が本文67.2％・図76.2％、③p.84のまとめで項目名が重複）。**あわせて、当方の成果品にあった項目名の取り違えを正した。**問36の54.1％は「相談窓口の充実」ではなく**「地域での見守りや声掛け」**であり、選択肢に「相談窓口の充実」は存在しない（素案・協議会資料・調査結果の分析・交付金の4点を訂正）。**点検の結果はOK 280件・NG 0件・説明のつく相違4件・一次資料が手元にないもの2件である。**相違はいずれも理由とともに記録している</t>
         </is>
       </c>
       <c r="O73" s="19" t="inlineStr">
         <is>
-          <t>**足りない図6件のうち、10月4日に要介護度の維持・改善を作成し、残りは2件になった。****いずれも町データ待ちである。**地域ケア会議の開催回数・検討件数（町の事業実績待ち）と、介護給付適正化の主要3事業の実施状況（町の実施報告待ち）</t>
+          <t>**町データが届くたびに突合対象が増える。とくに成果指標の現状値17項目と令和7年度決算が入ると、素案・算定シート・協議会資料の3系統を同時に照合する必要がある**</t>
         </is>
       </c>
       <c r="P73" s="24" t="n"/>
@@ -14340,32 +14402,32 @@
       </c>
       <c r="B74" s="20" t="inlineStr">
         <is>
-          <t>11-3</t>
+          <t>11-2</t>
         </is>
       </c>
       <c r="C74" s="19" t="inlineStr">
         <is>
-          <t>図表の追加作成</t>
+          <t>図表データ管理台帳の整備と運用</t>
         </is>
       </c>
       <c r="D74" s="19" t="inlineStr">
         <is>
-          <t>交付金の評価結果・調査結果の裏づけとなる図の作成</t>
+          <t>成果品に載せる図表の出所・算定根拠・差し込み先を1枚で追えるようにする</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr">
         <is>
-          <t>B1 現状分析（基礎データ・資料の整理分析）</t>
+          <t>B10 業務管理・計画の基本的な考え方</t>
         </is>
       </c>
       <c r="F74" s="20" t="inlineStr">
         <is>
-          <t>仕様書4(1)</t>
+          <t>仕様書全般</t>
         </is>
       </c>
       <c r="G74" s="19" t="inlineStr">
         <is>
-          <t>【4(1)】基礎的な地域データ及び資料の整理分析（現状分析）。高齢者福祉・介護保険をめぐる施策の動向、小野町の概要及び社会経済的特性、地域福祉資源の整備状況、高齢者の現況動向及びサービスの利用状況等について、小野町が提供するデータをもとに整理分析を行う。（計画策定の検討資料として活用するため、各種事項の将来推計を行う。なお、推計にあたっては、可能な限り細分化する）</t>
+          <t>【全般】委託仕様書及び公告の全体（成果品要件・工程・作業分担の確認）</t>
         </is>
       </c>
       <c r="H74" s="20" t="inlineStr">
@@ -14380,7 +14442,7 @@
       </c>
       <c r="J74" s="20" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="K74" s="23" t="inlineStr">
@@ -14389,19 +14451,19 @@
         </is>
       </c>
       <c r="L74" s="22" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="M74" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>**台帳が洗い出した「足りない図」のうち4点を作成した。****①入院時・退院時の加算算定率（f46）**── 支援Ⅲの失点の中身を示す図。**②認知症施策の体制と活動（f47）**── 推進員1→4人、カフェ1か所で横ばい、初期集中支援チームの訪問実績0件。体制は県内の標準を満たすが活動実績が伴っていないことが1枚で分かる。**③通いの場（f48）**── 見える化の箇所数（平成28年度以降0か所）と調査の参加頻度（年に数回以上13.8％）を並べ、食い違いを可視化した。**④要介護度の維持・改善（f49）**── 成果指標群（目標Ⅳ）の指標別得点を令和6年度交付金と令和8年度で並べ、0点のまま残る健康寿命延伸の状況の中身（要介護2以上の認定率）を添えた。**10月4日に作成し、給付適正化と交付金の取りまとめ 第2章(4)に差し込んだ。**いずれも素案・協議会資料・交付金の取りまとめに差し込み済み</t>
+          <t>**9月30日に図表データ管理台帳（25シート）を新設した（22_図表管理）。**図22点の差し込み先、交付金の評価指標との紐付け11件、成果品9件との対応、足りない図6件を一覧にしている。**台帳の数値は ono_figs.py の共通出口から自動で控える仕組みにした**（matplotlib の描画オブジェクトから系列名と数値を読み取り、_ledger.json に書き出す）。手で転記しないため、図と台帳がずれない。**小野町は図を一次資料から毎回計算する作りであるため、台帳は正本ではなく控えである旨を00シートに明記した**</t>
         </is>
       </c>
       <c r="O74" s="19" t="inlineStr">
         <is>
-          <t>**残る2点はいずれも町データ待ち。地域ケア会議の開催回数・検討件数と、介護給付適正化の主要3事業の実施状況である**</t>
+          <t>**足りない図6件のうち、10月4日に要介護度の維持・改善を作成し、残りは2件になった。****いずれも町データ待ちである。**地域ケア会議の開催回数・検討件数（町の事業実績待ち）と、介護給付適正化の主要3事業の実施状況（町の実施報告待ち）</t>
         </is>
       </c>
       <c r="P74" s="24" t="n"/>
@@ -14421,32 +14483,32 @@
       </c>
       <c r="B75" s="20" t="inlineStr">
         <is>
-          <t>11-4</t>
+          <t>11-3</t>
         </is>
       </c>
       <c r="C75" s="19" t="inlineStr">
         <is>
-          <t>成果品の体裁の統一と機械点検</t>
+          <t>図表の追加作成</t>
         </is>
       </c>
       <c r="D75" s="19" t="inlineStr">
         <is>
-          <t>書体・余白・見出し・表の体裁をそろえ、崩れを機械で検出する</t>
+          <t>交付金の評価結果・調査結果の裏づけとなる図の作成</t>
         </is>
       </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t>B9 成果品の納品</t>
+          <t>B1 現状分析（基礎データ・資料の整理分析）</t>
         </is>
       </c>
       <c r="F75" s="20" t="inlineStr">
         <is>
-          <t>仕様書4 成果品</t>
+          <t>仕様書4(1)</t>
         </is>
       </c>
       <c r="G75" s="19" t="inlineStr">
         <is>
-          <t>【成果品】（1）〜（4）のデータ（CD-R）1部、冊子（簡易製本）各3部／（5）（6）のデータ（CD-R）1部、計画書印刷50部／概要版印刷50部</t>
+          <t>【4(1)】基礎的な地域データ及び資料の整理分析（現状分析）。高齢者福祉・介護保険をめぐる施策の動向、小野町の概要及び社会経済的特性、地域福祉資源の整備状況、高齢者の現況動向及びサービスの利用状況等について、小野町が提供するデータをもとに整理分析を行う。（計画策定の検討資料として活用するため、各種事項の将来推計を行う。なお、推計にあたっては、可能な限り細分化する）</t>
         </is>
       </c>
       <c r="H75" s="20" t="inlineStr">
@@ -14477,12 +14539,12 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>**9月29日に ono_style.py の書体定数を改め、成果品全体を游ゴシック10.5ptにそろえた。****強調記法（**）がそのまま読み手に見えていた不具合を直した**（見える化突合の資料が共通スタイルを通らず独自に組んでいたため、docx 3件・xlsx 18件で記号が露出していた）。**体裁の点検は check_ono_taisai.py で行う**（この環境ではLibreOfficeが動かずPDFで目視できないため、docx・xlsx を直接読んで点検する）。**番号の通し確認を自己点検に加え、打合せ資料の要点・依頼資料・配布資料の番号の乱れ3件を検出して直した**</t>
+          <t>**台帳が洗い出した「足りない図」のうち4点を作成した。****①入院時・退院時の加算算定率（f46）**── 支援Ⅲの失点の中身を示す図。**②認知症施策の体制と活動（f47）**── 推進員1→4人、カフェ1か所で横ばい、初期集中支援チームの訪問実績0件。体制は県内の標準を満たすが活動実績が伴っていないことが1枚で分かる。**③通いの場（f48）**── 見える化の箇所数（平成28年度以降0か所）と調査の参加頻度（年に数回以上13.8％）を並べ、食い違いを可視化した。**④要介護度の維持・改善（f49）**── 成果指標群（目標Ⅳ）の指標別得点を令和6年度交付金と令和8年度で並べ、0点のまま残る健康寿命延伸の状況の中身（要介護2以上の認定率）を添えた。**10月4日に作成し、給付適正化と交付金の取りまとめ 第2章(4)に差し込んだ。**いずれも素案・協議会資料・交付金の取りまとめに差し込み済み</t>
         </is>
       </c>
       <c r="O75" s="19" t="inlineStr">
         <is>
-          <t>**印刷用の最終体裁（4色刷り・80頁）は組版工程（10-2）で別に点検する**</t>
+          <t>**残る2点はいずれも町データ待ち。地域ケア会議の開催回数・検討件数と、介護給付適正化の主要3事業の実施状況である**</t>
         </is>
       </c>
       <c r="P75" s="24" t="n"/>
@@ -14502,32 +14564,32 @@
       </c>
       <c r="B76" s="20" t="inlineStr">
         <is>
-          <t>11-5</t>
+          <t>11-4</t>
         </is>
       </c>
       <c r="C76" s="19" t="inlineStr">
         <is>
-          <t>他団体の資料・データの取扱いの点検</t>
+          <t>成果品の体裁の統一と機械点検</t>
         </is>
       </c>
       <c r="D76" s="19" t="inlineStr">
         <is>
-          <t>他団体から受領していない資料の数値・団体名が成果品に混入していないかの全件走査</t>
+          <t>書体・余白・見出し・表の体裁をそろえ、崩れを機械で検出する</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr">
         <is>
-          <t>B10 業務管理・計画の基本的な考え方</t>
+          <t>B9 成果品の納品</t>
         </is>
       </c>
       <c r="F76" s="20" t="inlineStr">
         <is>
-          <t>仕様書全般</t>
+          <t>仕様書4 成果品</t>
         </is>
       </c>
       <c r="G76" s="19" t="inlineStr">
         <is>
-          <t>【全般】委託仕様書及び公告の全体（成果品要件・工程・作業分担の確認）</t>
+          <t>【成果品】（1）〜（4）のデータ（CD-R）1部、冊子（簡易製本）各3部／（5）（6）のデータ（CD-R）1部、計画書印刷50部／概要版印刷50部</t>
         </is>
       </c>
       <c r="H76" s="20" t="inlineStr">
@@ -14542,28 +14604,28 @@
       </c>
       <c r="J76" s="20" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="K76" s="21" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="K76" s="23" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="L76" s="22" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M76" s="23" t="n">
         <v>2</v>
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>**方法の参考にした他団体の案件について、団体名と個別の数値が当方の成果品に残っていないかを全件走査した。****当方作成の成果品36箇所と過去版11ファイルで検出し、すべて「他町村の案件」「他団体」または県内の分布（平均・中央値・四分位・最大・最小）と小野町の順位に置き換えた。****県内比較は福島県内59市町村に限り、個別の団体名と個別の得点は出さない。**走査を再実行し、検出0件を確認している</t>
+          <t>**9月29日に ono_style.py の書体定数を改め、成果品全体を游ゴシック10.5ptにそろえた。****強調記法（**）がそのまま読み手に見えていた不具合を直した**（見える化突合の資料が共通スタイルを通らず独自に組んでいたため、docx 3件・xlsx 18件で記号が露出していた）。**体裁の点検は check_ono_taisai.py で行う**（この環境ではLibreOfficeが動かずPDFで目視できないため、docx・xlsx を直接読んで点検する）。**番号の通し確認を自己点検に加え、打合せ資料の要点・依頼資料・配布資料の番号の乱れ3件を検出して直した**</t>
         </is>
       </c>
       <c r="O76" s="19" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**印刷用の最終体裁（4色刷り・80頁）は組版工程（10-2）で別に点検する**</t>
         </is>
       </c>
       <c r="P76" s="24" t="n"/>
@@ -14583,17 +14645,17 @@
       </c>
       <c r="B77" s="20" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>11-5</t>
         </is>
       </c>
       <c r="C77" s="19" t="inlineStr">
         <is>
-          <t>ペンディング項目の整理と作業順位の管理</t>
+          <t>他団体の資料・データの取扱いの点検</t>
         </is>
       </c>
       <c r="D77" s="19" t="inlineStr">
         <is>
-          <t>止まっている項目の影響度・優先順位と、止まっていない作業の着手順を1枚で追えるようにする</t>
+          <t>他団体から受領していない資料の数値・団体名が成果品に混入していないかの全件走査</t>
         </is>
       </c>
       <c r="E77" s="19" t="inlineStr">
@@ -14603,12 +14665,12 @@
       </c>
       <c r="F77" s="20" t="inlineStr">
         <is>
-          <t>仕様書5(3)</t>
+          <t>仕様書全般</t>
         </is>
       </c>
       <c r="G77" s="19" t="inlineStr">
         <is>
-          <t>【5(3)】本仕様書に定めのない事項及び疑義が生じた場合は、小野町と受託者で協議するものとする。</t>
+          <t>【全般】委託仕様書及び公告の全体（成果品要件・工程・作業分担の確認）</t>
         </is>
       </c>
       <c r="H77" s="20" t="inlineStr">
@@ -14618,33 +14680,33 @@
       </c>
       <c r="I77" s="20" t="inlineStr">
         <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="J77" s="20" t="inlineStr">
+        <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="J77" s="20" t="inlineStr">
-        <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="K77" s="23" t="inlineStr">
-        <is>
-          <t>進行中</t>
+      <c r="K77" s="21" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L77" s="22" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="M77" s="23" t="n">
         <v>2</v>
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>**10月1日にペンディング整理と作業順位を新設した（17_業務進捗管理）。****止まっている項目38件（町の政策判断11件・資料の提供21件・国・県の決定待ち6件）を影響度（保険料に直結11件／法定記載事項に直結11件／交付金の得点8件／記述の裏づけ8件）と緊急度から機械的に順位づけした。**町に係る項目は打合せ資料の決定依頼事項一覧から引いており、本ブックに書き写していない（打合せ資料に項目が増えれば現れる）。**国・県の決定待ち（介護報酬改定率・第1号被保険者負担割合・調整交付金の見込交付割合・制度改正の公布・県計画）は町に向けた一覧がないため本ブックで定義した。保険料に最も強く効くのはここで、負担割合1ポイントで月額269円動く。****全38件に「回答がない場合にどうするか」を置いた。**待っているだけの一覧は待ち時間を短くしないためである。**あわせて、町の回答を待たずに進められる作業14件・38.0時間を洗い出し、10月2日から8日までの着手順に落とした**（1日8.0時間を上限とし、超えると生成が止まる）。自己点検10項目</t>
+          <t>**方法の参考にした他団体の案件について、団体名と個別の数値が当方の成果品に残っていないかを全件走査した。****当方作成の成果品36箇所と過去版11ファイルで検出し、すべて「他町村の案件」「他団体」または県内の分布（平均・中央値・四分位・最大・最小）と小野町の順位に置き換えた。****県内比較は福島県内59市町村に限り、個別の団体名と個別の得点は出さない。**走査を再実行し、検出0件を確認している</t>
         </is>
       </c>
       <c r="O77" s="19" t="inlineStr">
         <is>
-          <t>**町の回答が届くたびに順位を組み替える。優先1位（基金運用状況調書）の回答が来た時点で、その日の作業を止めて差し替えに回す**</t>
+          <t>―</t>
         </is>
       </c>
       <c r="P77" s="24" t="n"/>
@@ -14656,9 +14718,90 @@
       <c r="V77" s="24" t="n"/>
       <c r="W77" s="24" t="n"/>
     </row>
+    <row r="78">
+      <c r="A78" s="19" t="inlineStr">
+        <is>
+          <t>P11 品質・進捗管理</t>
+        </is>
+      </c>
+      <c r="B78" s="20" t="inlineStr">
+        <is>
+          <t>11-6</t>
+        </is>
+      </c>
+      <c r="C78" s="19" t="inlineStr">
+        <is>
+          <t>ペンディング項目の整理と作業順位の管理</t>
+        </is>
+      </c>
+      <c r="D78" s="19" t="inlineStr">
+        <is>
+          <t>止まっている項目の影響度・優先順位と、止まっていない作業の着手順を1枚で追えるようにする</t>
+        </is>
+      </c>
+      <c r="E78" s="19" t="inlineStr">
+        <is>
+          <t>B10 業務管理・計画の基本的な考え方</t>
+        </is>
+      </c>
+      <c r="F78" s="20" t="inlineStr">
+        <is>
+          <t>仕様書5(3)</t>
+        </is>
+      </c>
+      <c r="G78" s="19" t="inlineStr">
+        <is>
+          <t>【5(3)】本仕様書に定めのない事項及び疑義が生じた場合は、小野町と受託者で協議するものとする。</t>
+        </is>
+      </c>
+      <c r="H78" s="20" t="inlineStr">
+        <is>
+          <t>受託者</t>
+        </is>
+      </c>
+      <c r="I78" s="20" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="J78" s="20" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="K78" s="23" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="L78" s="22" t="n">
+        <v>70</v>
+      </c>
+      <c r="M78" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="N78" s="19" t="inlineStr">
+        <is>
+          <t>**10月1日にペンディング整理と作業順位を新設した（17_業務進捗管理）。****止まっている項目38件（町の政策判断11件・資料の提供21件・国・県の決定待ち6件）を影響度（保険料に直結11件／法定記載事項に直結11件／交付金の得点8件／記述の裏づけ8件）と緊急度から機械的に順位づけした。**町に係る項目は打合せ資料の決定依頼事項一覧から引いており、本ブックに書き写していない（打合せ資料に項目が増えれば現れる）。**国・県の決定待ち（介護報酬改定率・第1号被保険者負担割合・調整交付金の見込交付割合・制度改正の公布・県計画）は町に向けた一覧がないため本ブックで定義した。保険料に最も強く効くのはここで、負担割合1ポイントで月額269円動く。****全38件に「回答がない場合にどうするか」を置いた。**待っているだけの一覧は待ち時間を短くしないためである。**あわせて、町の回答を待たずに進められる作業14件・38.0時間を洗い出し、10月2日から8日までの着手順に落とした**（1日8.0時間を上限とし、超えると生成が止まる）。自己点検10項目</t>
+        </is>
+      </c>
+      <c r="O78" s="19" t="inlineStr">
+        <is>
+          <t>**町の回答が届くたびに順位を組み替える。優先1位（基金運用状況調書）の回答が来た時点で、その日の作業を止めて差し替えに回す**</t>
+        </is>
+      </c>
+      <c r="P78" s="24" t="n"/>
+      <c r="Q78" s="24" t="n"/>
+      <c r="R78" s="24" t="n"/>
+      <c r="S78" s="24" t="n"/>
+      <c r="T78" s="24" t="n"/>
+      <c r="U78" s="24" t="n"/>
+      <c r="V78" s="24" t="n"/>
+      <c r="W78" s="24" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O77"/>
-  <conditionalFormatting sqref="L2:L77">
+  <autoFilter ref="A1:O78"/>
+  <conditionalFormatting sqref="L2:L78">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>100</formula>
     </cfRule>
@@ -14667,10 +14810,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="K2:K77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,進行中,要対応,データ待ち,未着手"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+    <dataValidation sqref="L2:L78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
@@ -14765,31 +14908,31 @@
         </is>
       </c>
       <c r="B2" s="20">
-        <f>COUNTIF('01_WBS'!$A$2:$A$77,$A2)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$78,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A2,'01_WBS'!$K$2:$K$77,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A2,'01_WBS'!$K$2:$K$78,"完了")</f>
         <v/>
       </c>
       <c r="D2" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A2,'01_WBS'!$K$2:$K$77,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A2,'01_WBS'!$K$2:$K$78,"進行中")</f>
         <v/>
       </c>
       <c r="E2" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A2,'01_WBS'!$K$2:$K$77,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A2,'01_WBS'!$K$2:$K$78,"要対応")</f>
         <v/>
       </c>
       <c r="F2" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A2,'01_WBS'!$K$2:$K$77,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A2,'01_WBS'!$K$2:$K$78,"データ待ち")</f>
         <v/>
       </c>
       <c r="G2" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A2,'01_WBS'!$K$2:$K$77,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A2,'01_WBS'!$K$2:$K$78,"未着手")</f>
         <v/>
       </c>
       <c r="H2" s="28">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A2)*'01_WBS'!$M$2:$M$77)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A2)*'01_WBS'!$L$2:$L$77*'01_WBS'!$M$2:$M$77)/SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A2)*'01_WBS'!$M$2:$M$77)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A2)*'01_WBS'!$M$2:$M$78)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A2)*'01_WBS'!$L$2:$L$78*'01_WBS'!$M$2:$M$78)/SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A2)*'01_WBS'!$M$2:$M$78)/100)</f>
         <v/>
       </c>
       <c r="I2" s="20" t="inlineStr">
@@ -14815,31 +14958,31 @@
         </is>
       </c>
       <c r="B3" s="20">
-        <f>COUNTIF('01_WBS'!$A$2:$A$77,$A3)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$78,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A3,'01_WBS'!$K$2:$K$77,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A3,'01_WBS'!$K$2:$K$78,"完了")</f>
         <v/>
       </c>
       <c r="D3" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A3,'01_WBS'!$K$2:$K$77,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A3,'01_WBS'!$K$2:$K$78,"進行中")</f>
         <v/>
       </c>
       <c r="E3" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A3,'01_WBS'!$K$2:$K$77,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A3,'01_WBS'!$K$2:$K$78,"要対応")</f>
         <v/>
       </c>
       <c r="F3" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A3,'01_WBS'!$K$2:$K$77,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A3,'01_WBS'!$K$2:$K$78,"データ待ち")</f>
         <v/>
       </c>
       <c r="G3" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A3,'01_WBS'!$K$2:$K$77,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A3,'01_WBS'!$K$2:$K$78,"未着手")</f>
         <v/>
       </c>
       <c r="H3" s="28">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A3)*'01_WBS'!$M$2:$M$77)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A3)*'01_WBS'!$L$2:$L$77*'01_WBS'!$M$2:$M$77)/SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A3)*'01_WBS'!$M$2:$M$77)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A3)*'01_WBS'!$M$2:$M$78)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A3)*'01_WBS'!$L$2:$L$78*'01_WBS'!$M$2:$M$78)/SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A3)*'01_WBS'!$M$2:$M$78)/100)</f>
         <v/>
       </c>
       <c r="I3" s="20" t="inlineStr">
@@ -14865,31 +15008,31 @@
         </is>
       </c>
       <c r="B4" s="20">
-        <f>COUNTIF('01_WBS'!$A$2:$A$77,$A4)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$78,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A4,'01_WBS'!$K$2:$K$77,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A4,'01_WBS'!$K$2:$K$78,"完了")</f>
         <v/>
       </c>
       <c r="D4" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A4,'01_WBS'!$K$2:$K$77,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A4,'01_WBS'!$K$2:$K$78,"進行中")</f>
         <v/>
       </c>
       <c r="E4" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A4,'01_WBS'!$K$2:$K$77,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A4,'01_WBS'!$K$2:$K$78,"要対応")</f>
         <v/>
       </c>
       <c r="F4" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A4,'01_WBS'!$K$2:$K$77,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A4,'01_WBS'!$K$2:$K$78,"データ待ち")</f>
         <v/>
       </c>
       <c r="G4" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A4,'01_WBS'!$K$2:$K$77,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A4,'01_WBS'!$K$2:$K$78,"未着手")</f>
         <v/>
       </c>
       <c r="H4" s="28">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A4)*'01_WBS'!$M$2:$M$77)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A4)*'01_WBS'!$L$2:$L$77*'01_WBS'!$M$2:$M$77)/SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A4)*'01_WBS'!$M$2:$M$77)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A4)*'01_WBS'!$M$2:$M$78)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A4)*'01_WBS'!$L$2:$L$78*'01_WBS'!$M$2:$M$78)/SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A4)*'01_WBS'!$M$2:$M$78)/100)</f>
         <v/>
       </c>
       <c r="I4" s="20" t="inlineStr">
@@ -14915,31 +15058,31 @@
         </is>
       </c>
       <c r="B5" s="20">
-        <f>COUNTIF('01_WBS'!$A$2:$A$77,$A5)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$78,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A5,'01_WBS'!$K$2:$K$77,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A5,'01_WBS'!$K$2:$K$78,"完了")</f>
         <v/>
       </c>
       <c r="D5" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A5,'01_WBS'!$K$2:$K$77,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A5,'01_WBS'!$K$2:$K$78,"進行中")</f>
         <v/>
       </c>
       <c r="E5" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A5,'01_WBS'!$K$2:$K$77,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A5,'01_WBS'!$K$2:$K$78,"要対応")</f>
         <v/>
       </c>
       <c r="F5" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A5,'01_WBS'!$K$2:$K$77,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A5,'01_WBS'!$K$2:$K$78,"データ待ち")</f>
         <v/>
       </c>
       <c r="G5" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A5,'01_WBS'!$K$2:$K$77,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A5,'01_WBS'!$K$2:$K$78,"未着手")</f>
         <v/>
       </c>
       <c r="H5" s="28">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A5)*'01_WBS'!$M$2:$M$77)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A5)*'01_WBS'!$L$2:$L$77*'01_WBS'!$M$2:$M$77)/SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A5)*'01_WBS'!$M$2:$M$77)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A5)*'01_WBS'!$M$2:$M$78)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A5)*'01_WBS'!$L$2:$L$78*'01_WBS'!$M$2:$M$78)/SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A5)*'01_WBS'!$M$2:$M$78)/100)</f>
         <v/>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -14965,31 +15108,31 @@
         </is>
       </c>
       <c r="B6" s="20">
-        <f>COUNTIF('01_WBS'!$A$2:$A$77,$A6)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$78,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A6,'01_WBS'!$K$2:$K$77,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A6,'01_WBS'!$K$2:$K$78,"完了")</f>
         <v/>
       </c>
       <c r="D6" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A6,'01_WBS'!$K$2:$K$77,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A6,'01_WBS'!$K$2:$K$78,"進行中")</f>
         <v/>
       </c>
       <c r="E6" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A6,'01_WBS'!$K$2:$K$77,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A6,'01_WBS'!$K$2:$K$78,"要対応")</f>
         <v/>
       </c>
       <c r="F6" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A6,'01_WBS'!$K$2:$K$77,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A6,'01_WBS'!$K$2:$K$78,"データ待ち")</f>
         <v/>
       </c>
       <c r="G6" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A6,'01_WBS'!$K$2:$K$77,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A6,'01_WBS'!$K$2:$K$78,"未着手")</f>
         <v/>
       </c>
       <c r="H6" s="28">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A6)*'01_WBS'!$M$2:$M$77)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A6)*'01_WBS'!$L$2:$L$77*'01_WBS'!$M$2:$M$77)/SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A6)*'01_WBS'!$M$2:$M$77)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A6)*'01_WBS'!$M$2:$M$78)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A6)*'01_WBS'!$L$2:$L$78*'01_WBS'!$M$2:$M$78)/SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A6)*'01_WBS'!$M$2:$M$78)/100)</f>
         <v/>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -15015,31 +15158,31 @@
         </is>
       </c>
       <c r="B7" s="20">
-        <f>COUNTIF('01_WBS'!$A$2:$A$77,$A7)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$78,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A7,'01_WBS'!$K$2:$K$77,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A7,'01_WBS'!$K$2:$K$78,"完了")</f>
         <v/>
       </c>
       <c r="D7" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A7,'01_WBS'!$K$2:$K$77,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A7,'01_WBS'!$K$2:$K$78,"進行中")</f>
         <v/>
       </c>
       <c r="E7" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A7,'01_WBS'!$K$2:$K$77,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A7,'01_WBS'!$K$2:$K$78,"要対応")</f>
         <v/>
       </c>
       <c r="F7" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A7,'01_WBS'!$K$2:$K$77,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A7,'01_WBS'!$K$2:$K$78,"データ待ち")</f>
         <v/>
       </c>
       <c r="G7" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A7,'01_WBS'!$K$2:$K$77,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A7,'01_WBS'!$K$2:$K$78,"未着手")</f>
         <v/>
       </c>
       <c r="H7" s="28">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A7)*'01_WBS'!$M$2:$M$77)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A7)*'01_WBS'!$L$2:$L$77*'01_WBS'!$M$2:$M$77)/SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A7)*'01_WBS'!$M$2:$M$77)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A7)*'01_WBS'!$M$2:$M$78)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A7)*'01_WBS'!$L$2:$L$78*'01_WBS'!$M$2:$M$78)/SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A7)*'01_WBS'!$M$2:$M$78)/100)</f>
         <v/>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -15065,31 +15208,31 @@
         </is>
       </c>
       <c r="B8" s="20">
-        <f>COUNTIF('01_WBS'!$A$2:$A$77,$A8)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$78,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A8,'01_WBS'!$K$2:$K$77,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A8,'01_WBS'!$K$2:$K$78,"完了")</f>
         <v/>
       </c>
       <c r="D8" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A8,'01_WBS'!$K$2:$K$77,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A8,'01_WBS'!$K$2:$K$78,"進行中")</f>
         <v/>
       </c>
       <c r="E8" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A8,'01_WBS'!$K$2:$K$77,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A8,'01_WBS'!$K$2:$K$78,"要対応")</f>
         <v/>
       </c>
       <c r="F8" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A8,'01_WBS'!$K$2:$K$77,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A8,'01_WBS'!$K$2:$K$78,"データ待ち")</f>
         <v/>
       </c>
       <c r="G8" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A8,'01_WBS'!$K$2:$K$77,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A8,'01_WBS'!$K$2:$K$78,"未着手")</f>
         <v/>
       </c>
       <c r="H8" s="28">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A8)*'01_WBS'!$M$2:$M$77)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A8)*'01_WBS'!$L$2:$L$77*'01_WBS'!$M$2:$M$77)/SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A8)*'01_WBS'!$M$2:$M$77)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A8)*'01_WBS'!$M$2:$M$78)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A8)*'01_WBS'!$L$2:$L$78*'01_WBS'!$M$2:$M$78)/SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A8)*'01_WBS'!$M$2:$M$78)/100)</f>
         <v/>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -15115,31 +15258,31 @@
         </is>
       </c>
       <c r="B9" s="20">
-        <f>COUNTIF('01_WBS'!$A$2:$A$77,$A9)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$78,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A9,'01_WBS'!$K$2:$K$77,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A9,'01_WBS'!$K$2:$K$78,"完了")</f>
         <v/>
       </c>
       <c r="D9" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A9,'01_WBS'!$K$2:$K$77,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A9,'01_WBS'!$K$2:$K$78,"進行中")</f>
         <v/>
       </c>
       <c r="E9" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A9,'01_WBS'!$K$2:$K$77,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A9,'01_WBS'!$K$2:$K$78,"要対応")</f>
         <v/>
       </c>
       <c r="F9" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A9,'01_WBS'!$K$2:$K$77,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A9,'01_WBS'!$K$2:$K$78,"データ待ち")</f>
         <v/>
       </c>
       <c r="G9" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A9,'01_WBS'!$K$2:$K$77,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A9,'01_WBS'!$K$2:$K$78,"未着手")</f>
         <v/>
       </c>
       <c r="H9" s="28">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A9)*'01_WBS'!$M$2:$M$77)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A9)*'01_WBS'!$L$2:$L$77*'01_WBS'!$M$2:$M$77)/SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A9)*'01_WBS'!$M$2:$M$77)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A9)*'01_WBS'!$M$2:$M$78)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A9)*'01_WBS'!$L$2:$L$78*'01_WBS'!$M$2:$M$78)/SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A9)*'01_WBS'!$M$2:$M$78)/100)</f>
         <v/>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -15165,31 +15308,31 @@
         </is>
       </c>
       <c r="B10" s="20">
-        <f>COUNTIF('01_WBS'!$A$2:$A$77,$A10)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$78,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A10,'01_WBS'!$K$2:$K$77,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A10,'01_WBS'!$K$2:$K$78,"完了")</f>
         <v/>
       </c>
       <c r="D10" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A10,'01_WBS'!$K$2:$K$77,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A10,'01_WBS'!$K$2:$K$78,"進行中")</f>
         <v/>
       </c>
       <c r="E10" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A10,'01_WBS'!$K$2:$K$77,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A10,'01_WBS'!$K$2:$K$78,"要対応")</f>
         <v/>
       </c>
       <c r="F10" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A10,'01_WBS'!$K$2:$K$77,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A10,'01_WBS'!$K$2:$K$78,"データ待ち")</f>
         <v/>
       </c>
       <c r="G10" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A10,'01_WBS'!$K$2:$K$77,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A10,'01_WBS'!$K$2:$K$78,"未着手")</f>
         <v/>
       </c>
       <c r="H10" s="28">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A10)*'01_WBS'!$M$2:$M$77)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A10)*'01_WBS'!$L$2:$L$77*'01_WBS'!$M$2:$M$77)/SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A10)*'01_WBS'!$M$2:$M$77)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A10)*'01_WBS'!$M$2:$M$78)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A10)*'01_WBS'!$L$2:$L$78*'01_WBS'!$M$2:$M$78)/SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A10)*'01_WBS'!$M$2:$M$78)/100)</f>
         <v/>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -15215,31 +15358,31 @@
         </is>
       </c>
       <c r="B11" s="20">
-        <f>COUNTIF('01_WBS'!$A$2:$A$77,$A11)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$78,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A11,'01_WBS'!$K$2:$K$77,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A11,'01_WBS'!$K$2:$K$78,"完了")</f>
         <v/>
       </c>
       <c r="D11" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A11,'01_WBS'!$K$2:$K$77,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A11,'01_WBS'!$K$2:$K$78,"進行中")</f>
         <v/>
       </c>
       <c r="E11" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A11,'01_WBS'!$K$2:$K$77,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A11,'01_WBS'!$K$2:$K$78,"要対応")</f>
         <v/>
       </c>
       <c r="F11" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A11,'01_WBS'!$K$2:$K$77,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A11,'01_WBS'!$K$2:$K$78,"データ待ち")</f>
         <v/>
       </c>
       <c r="G11" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A11,'01_WBS'!$K$2:$K$77,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A11,'01_WBS'!$K$2:$K$78,"未着手")</f>
         <v/>
       </c>
       <c r="H11" s="28">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A11)*'01_WBS'!$M$2:$M$77)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A11)*'01_WBS'!$L$2:$L$77*'01_WBS'!$M$2:$M$77)/SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A11)*'01_WBS'!$M$2:$M$77)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A11)*'01_WBS'!$M$2:$M$78)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A11)*'01_WBS'!$L$2:$L$78*'01_WBS'!$M$2:$M$78)/SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A11)*'01_WBS'!$M$2:$M$78)/100)</f>
         <v/>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -15265,31 +15408,31 @@
         </is>
       </c>
       <c r="B12" s="20">
-        <f>COUNTIF('01_WBS'!$A$2:$A$77,$A12)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$78,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A12,'01_WBS'!$K$2:$K$77,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A12,'01_WBS'!$K$2:$K$78,"完了")</f>
         <v/>
       </c>
       <c r="D12" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A12,'01_WBS'!$K$2:$K$77,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A12,'01_WBS'!$K$2:$K$78,"進行中")</f>
         <v/>
       </c>
       <c r="E12" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A12,'01_WBS'!$K$2:$K$77,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A12,'01_WBS'!$K$2:$K$78,"要対応")</f>
         <v/>
       </c>
       <c r="F12" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A12,'01_WBS'!$K$2:$K$77,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A12,'01_WBS'!$K$2:$K$78,"データ待ち")</f>
         <v/>
       </c>
       <c r="G12" s="20">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$77,$A12,'01_WBS'!$K$2:$K$77,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$78,$A12,'01_WBS'!$K$2:$K$78,"未着手")</f>
         <v/>
       </c>
       <c r="H12" s="28">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A12)*'01_WBS'!$M$2:$M$77)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A12)*'01_WBS'!$L$2:$L$77*'01_WBS'!$M$2:$M$77)/SUMPRODUCT(('01_WBS'!$A$2:$A$77=$A12)*'01_WBS'!$M$2:$M$77)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A12)*'01_WBS'!$M$2:$M$78)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A12)*'01_WBS'!$L$2:$L$78*'01_WBS'!$M$2:$M$78)/SUMPRODUCT(('01_WBS'!$A$2:$A$78=$A12)*'01_WBS'!$M$2:$M$78)/100)</f>
         <v/>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -15339,7 +15482,7 @@
         <v/>
       </c>
       <c r="H13" s="31">
-        <f>IF(SUM('01_WBS'!$M$2:$M$77)=0,0,SUMPRODUCT('01_WBS'!$L$2:$L$77,'01_WBS'!$M$2:$M$77)/SUM('01_WBS'!$M$2:$M$77)/100)</f>
+        <f>IF(SUM('01_WBS'!$M$2:$M$78)=0,0,SUMPRODUCT('01_WBS'!$L$2:$L$78,'01_WBS'!$M$2:$M$78)/SUM('01_WBS'!$M$2:$M$78)/100)</f>
         <v/>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -15975,7 +16118,7 @@
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
-          <t>**12月までに発注しないと2月の校了に間に合わない**</t>
+          <t>**年度末は印刷が集中するため1月中に業者を押さえる**</t>
         </is>
       </c>
     </row>
@@ -17514,7 +17657,7 @@
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
-          <t>**逆算表を作成済み（令和9年2月下旬の校了が期限）。12月までに印刷業者を押さえる**</t>
+          <t>**発注仕様書と見積依頼の様式を作成済み。年度末の印刷の集中を見て1月中に業者を押さえる**</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20261005.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20261005.xlsx
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.5492474226804124</v>
+        <v>0.5477731958762886</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.7033505154639176</v>
+        <v>0.7074742268041238</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -722,13 +722,13 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.1541030927835052</v>
+        <v>0.1597010309278351</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>おおむね予定どおり 46件／前倒し 23件／遅れ 4件／期限超過（2か月） 2件／期限超過（1か月） 2件</t>
+          <t>おおむね予定どおり 44件／前倒し 25件／遅れ 4件／期限超過（2か月） 2件／期限超過（1か月） 2件</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="B35" s="20" t="inlineStr">
         <is>
-          <t>9-3</t>
+          <t>9-4</t>
         </is>
       </c>
       <c r="C35" s="19" t="inlineStr">
         <is>
-          <t>協議会 第2回（骨子案・見込量・保険料・成果指標）</t>
+          <t>協議会 第3回（素案）</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E35" s="20" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G35" s="27" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="M35" s="19" t="inlineStr">
         <is>
-          <t>P7の完了、開催日の確定</t>
+          <t>素案の確定</t>
         </is>
       </c>
     </row>
@@ -5812,39 +5812,39 @@
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>9-4</t>
+          <t>9-5</t>
         </is>
       </c>
       <c r="C36" s="19" t="inlineStr">
         <is>
-          <t>協議会 第3回（素案）</t>
+          <t>パブリックコメントの様式作成</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="G36" s="27" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G36" s="21" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H36" s="32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I36" s="32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J36" s="32" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="M36" s="19" t="inlineStr">
         <is>
-          <t>素案の確定</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -5871,39 +5871,39 @@
       </c>
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>9-5</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="C37" s="19" t="inlineStr">
         <is>
-          <t>パブリックコメントの様式作成</t>
+          <t>パブリックコメントの実施</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>町</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="F37" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="G37" s="21" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="G37" s="27" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H37" s="32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I37" s="32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J37" s="32" t="n">
         <v>0</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="M37" s="19" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>素案の確定、実施時期の確定（依頼票C6）</t>
         </is>
       </c>
     </row>
@@ -5930,27 +5930,27 @@
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="C38" s="19" t="inlineStr">
         <is>
-          <t>パブリックコメントの実施</t>
+          <t>意見への対応</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G38" s="27" t="inlineStr">
@@ -5977,29 +5977,29 @@
       </c>
       <c r="M38" s="19" t="inlineStr">
         <is>
-          <t>素案の確定、実施時期の確定（依頼票C6）</t>
+          <t>パブコメの実施</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="19" t="inlineStr">
         <is>
-          <t>P9 意見聴取</t>
+          <t>P10 完成・納品</t>
         </is>
       </c>
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>10-3</t>
         </is>
       </c>
       <c r="C39" s="19" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>校正（初校・再校・校了）</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E39" s="20" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="M39" s="19" t="inlineStr">
         <is>
-          <t>パブコメの実施</t>
+          <t>組版</t>
         </is>
       </c>
     </row>
@@ -6048,17 +6048,17 @@
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>10-3</t>
+          <t>10-5</t>
         </is>
       </c>
       <c r="C40" s="19" t="inlineStr">
         <is>
-          <t>校正（初校・再校・校了）</t>
+          <t>概要版の作成</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E40" s="20" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="F40" s="20" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G40" s="27" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="M40" s="19" t="inlineStr">
         <is>
-          <t>組版</t>
+          <t>計画書の確定</t>
         </is>
       </c>
     </row>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>10-5</t>
+          <t>10-6</t>
         </is>
       </c>
       <c r="C41" s="19" t="inlineStr">
         <is>
-          <t>概要版の作成</t>
+          <t>印刷・製本</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="E41" s="20" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="F41" s="20" t="inlineStr">
@@ -6154,24 +6154,24 @@
       </c>
       <c r="M41" s="19" t="inlineStr">
         <is>
-          <t>計画書の確定</t>
+          <t>校了</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t>P10 完成・納品</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>10-6</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C42" s="19" t="inlineStr">
         <is>
-          <t>印刷・製本</t>
+          <t>第1号被保険者の分析</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
@@ -6181,30 +6181,30 @@
       </c>
       <c r="E42" s="20" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F42" s="20" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="G42" s="27" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G42" s="21" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H42" s="32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I42" s="32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J42" s="32" t="n">
         <v>0</v>
       </c>
       <c r="K42" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L42" s="21" t="inlineStr">
         <is>
@@ -6213,24 +6213,24 @@
       </c>
       <c r="M42" s="19" t="inlineStr">
         <is>
-          <t>校了</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="19" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P3 給付費等の分析</t>
         </is>
       </c>
       <c r="B43" s="20" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>3-3</t>
         </is>
       </c>
       <c r="C43" s="19" t="inlineStr">
         <is>
-          <t>第1号被保険者の分析</t>
+          <t>成果品①の製本・納品</t>
         </is>
       </c>
       <c r="D43" s="20" t="inlineStr">
@@ -6240,24 +6240,24 @@
       </c>
       <c r="E43" s="20" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="F43" s="20" t="inlineStr">
         <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="G43" s="21" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="G43" s="27" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H43" s="32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I43" s="32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J43" s="32" t="n">
         <v>0</v>
@@ -6272,24 +6272,24 @@
       </c>
       <c r="M43" s="19" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>報告書の確定</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="19" t="inlineStr">
         <is>
-          <t>P3 給付費等の分析</t>
+          <t>P4 調査結果の反映</t>
         </is>
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>3-3</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C44" s="19" t="inlineStr">
         <is>
-          <t>成果品①の製本・納品</t>
+          <t>レッドチームレビュー</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
@@ -6299,24 +6299,24 @@
       </c>
       <c r="E44" s="20" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F44" s="20" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="G44" s="27" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G44" s="21" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H44" s="32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I44" s="32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J44" s="32" t="n">
         <v>0</v>
@@ -6331,24 +6331,24 @@
       </c>
       <c r="M44" s="19" t="inlineStr">
         <is>
-          <t>報告書の確定</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="19" t="inlineStr">
         <is>
-          <t>P4 調査結果の反映</t>
+          <t>P6 骨子案</t>
         </is>
       </c>
       <c r="B45" s="20" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>6-3</t>
         </is>
       </c>
       <c r="C45" s="19" t="inlineStr">
         <is>
-          <t>レッドチームレビュー</t>
+          <t>成果品③の製本・納品</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
@@ -6358,24 +6358,24 @@
       </c>
       <c r="E45" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="F45" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="G45" s="21" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="G45" s="27" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H45" s="32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I45" s="32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J45" s="32" t="n">
         <v>0</v>
@@ -6390,24 +6390,24 @@
       </c>
       <c r="M45" s="19" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>骨子案の確定</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="19" t="inlineStr">
         <is>
-          <t>P6 骨子案</t>
+          <t>P7 推計・算定</t>
         </is>
       </c>
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>7-8</t>
         </is>
       </c>
       <c r="C46" s="19" t="inlineStr">
         <is>
-          <t>成果品③の製本・納品</t>
+          <t>成果品②の製本・納品</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
@@ -6449,24 +6449,24 @@
       </c>
       <c r="M46" s="19" t="inlineStr">
         <is>
-          <t>骨子案の確定</t>
+          <t>報告書の確定</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="19" t="inlineStr">
         <is>
-          <t>P7 推計・算定</t>
+          <t>P8 素案</t>
         </is>
       </c>
       <c r="B47" s="20" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>8-6</t>
         </is>
       </c>
       <c r="C47" s="19" t="inlineStr">
         <is>
-          <t>成果品②の製本・納品</t>
+          <t>成果品④の製本・納品</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
@@ -6508,39 +6508,39 @@
       </c>
       <c r="M47" s="19" t="inlineStr">
         <is>
-          <t>報告書の確定</t>
+          <t>素案の確定</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="19" t="inlineStr">
         <is>
-          <t>P8 素案</t>
+          <t>P9 意見聴取</t>
         </is>
       </c>
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>8-6</t>
+          <t>9-8</t>
         </is>
       </c>
       <c r="C48" s="19" t="inlineStr">
         <is>
-          <t>成果品④の製本・納品</t>
+          <t>協議会 第4回（最終案）</t>
         </is>
       </c>
       <c r="D48" s="20" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E48" s="20" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="F48" s="20" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G48" s="27" t="inlineStr">
@@ -6567,39 +6567,39 @@
       </c>
       <c r="M48" s="19" t="inlineStr">
         <is>
-          <t>素案の確定</t>
+          <t>意見への対応</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="19" t="inlineStr">
         <is>
-          <t>P9 意見聴取</t>
+          <t>P10 完成・納品</t>
         </is>
       </c>
       <c r="B49" s="20" t="inlineStr">
         <is>
-          <t>9-8</t>
+          <t>10-7</t>
         </is>
       </c>
       <c r="C49" s="19" t="inlineStr">
         <is>
-          <t>協議会 第4回（最終案）</t>
+          <t>データCD-Rの作成</t>
         </is>
       </c>
       <c r="D49" s="20" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E49" s="20" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="F49" s="20" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G49" s="27" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="M49" s="19" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>各成果品の確定</t>
         </is>
       </c>
     </row>
@@ -6638,39 +6638,39 @@
       </c>
       <c r="B50" s="20" t="inlineStr">
         <is>
-          <t>10-4</t>
+          <t>10-8</t>
         </is>
       </c>
       <c r="C50" s="19" t="inlineStr">
         <is>
-          <t>概要版の構成案</t>
+          <t>納品・検収</t>
         </is>
       </c>
       <c r="D50" s="20" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E50" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="F50" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="G50" s="21" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="G50" s="27" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H50" s="32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I50" s="32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J50" s="32" t="n">
         <v>0</v>
@@ -6685,24 +6685,24 @@
       </c>
       <c r="M50" s="19" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>全成果品の完成</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="19" t="inlineStr">
         <is>
-          <t>P10 完成・納品</t>
+          <t>P3 給付費等の分析</t>
         </is>
       </c>
       <c r="B51" s="20" t="inlineStr">
         <is>
-          <t>10-7</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C51" s="19" t="inlineStr">
         <is>
-          <t>データCD-Rの作成</t>
+          <t>給付費等分析結果報告書の作成</t>
         </is>
       </c>
       <c r="D51" s="20" t="inlineStr">
@@ -6712,30 +6712,30 @@
       </c>
       <c r="E51" s="20" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F51" s="20" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="G51" s="27" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="G51" s="23" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H51" s="32" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I51" s="32" t="n">
-        <v>0</v>
+        <v>63.2</v>
       </c>
       <c r="J51" s="32" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="K51" s="20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L51" s="21" t="inlineStr">
         <is>
@@ -6744,57 +6744,57 @@
       </c>
       <c r="M51" s="19" t="inlineStr">
         <is>
-          <t>各成果品の確定</t>
+          <t>町の給付実績（依頼票S1・S2）で数値を確定する</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="19" t="inlineStr">
         <is>
-          <t>P10 完成・納品</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="B52" s="20" t="inlineStr">
         <is>
-          <t>10-8</t>
+          <t>1-7</t>
         </is>
       </c>
       <c r="C52" s="19" t="inlineStr">
         <is>
-          <t>納品・検収</t>
+          <t>町データの受領</t>
         </is>
       </c>
       <c r="D52" s="20" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>町</t>
         </is>
       </c>
       <c r="E52" s="20" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F52" s="20" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="G52" s="27" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G52" s="23" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H52" s="32" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I52" s="32" t="n">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J52" s="32" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="K52" s="20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L52" s="21" t="inlineStr">
         <is>
@@ -6803,24 +6803,24 @@
       </c>
       <c r="M52" s="19" t="inlineStr">
         <is>
-          <t>全成果品の完成</t>
+          <t>**残るのは地域支援事業費の内訳（S6）、令和7年度決算（S7）、成果指標の現状値17項目（H1〜H17）、総合事業上限額算定の手引き、地域支援事業交付金事業実績報告書、令和6年度のケアプラン点検の実施件数**</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="19" t="inlineStr">
         <is>
-          <t>P3 給付費等の分析</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="B53" s="20" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2-9</t>
         </is>
       </c>
       <c r="C53" s="19" t="inlineStr">
         <is>
-          <t>給付費等分析結果報告書の作成</t>
+          <t>介護保険財政の分析</t>
         </is>
       </c>
       <c r="D53" s="20" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="E53" s="20" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F53" s="20" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G53" s="23" t="inlineStr">
@@ -6844,16 +6844,16 @@
         </is>
       </c>
       <c r="H53" s="32" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="I53" s="32" t="n">
-        <v>63.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J53" s="32" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="K53" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L53" s="21" t="inlineStr">
         <is>
@@ -6862,39 +6862,39 @@
       </c>
       <c r="M53" s="19" t="inlineStr">
         <is>
-          <t>町の給付実績（依頼票S1・S2）で数値を確定する</t>
+          <t>**令和7年度の様式4が全て0で未入力。また基金保有額が令和4年度末120百万円から令和5年度末12百万円へ1桁減っており、取崩実績か入力誤りかの確認が要る**</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="19" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P6 骨子案</t>
         </is>
       </c>
       <c r="B54" s="20" t="inlineStr">
         <is>
-          <t>1-7</t>
+          <t>6-1</t>
         </is>
       </c>
       <c r="C54" s="19" t="inlineStr">
         <is>
-          <t>町データの受領</t>
+          <t>骨子案の作成</t>
         </is>
       </c>
       <c r="D54" s="20" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E54" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F54" s="20" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="G54" s="23" t="inlineStr">
@@ -6906,54 +6906,54 @@
         <v>80</v>
       </c>
       <c r="I54" s="32" t="n">
-        <v>71.40000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="J54" s="32" t="n">
-        <v>8.6</v>
+        <v>16.8</v>
       </c>
       <c r="K54" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="L54" s="21" t="inlineStr">
-        <is>
-          <t>おおむね予定どおり</t>
+      <c r="L54" s="33" t="inlineStr">
+        <is>
+          <t>前倒し</t>
         </is>
       </c>
       <c r="M54" s="19" t="inlineStr">
         <is>
-          <t>**残るのは地域支援事業費の内訳（S6）、令和7年度決算（S7）、成果指標の現状値17項目（H1〜H17）、総合事業上限額算定の手引き、地域支援事業交付金事業実績報告書、令和6年度のケアプラン点検の実施件数**</t>
+          <t>実績データによる数値の確定</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="19" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P8 素案</t>
         </is>
       </c>
       <c r="B55" s="20" t="inlineStr">
         <is>
-          <t>2-9</t>
+          <t>8-8</t>
         </is>
       </c>
       <c r="C55" s="19" t="inlineStr">
         <is>
-          <t>介護保険財政の分析</t>
+          <t>在宅医療・介護連携の目指すべき姿の設定</t>
         </is>
       </c>
       <c r="D55" s="20" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E55" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F55" s="20" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G55" s="23" t="inlineStr">
@@ -6962,42 +6962,42 @@
         </is>
       </c>
       <c r="H55" s="32" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="I55" s="32" t="n">
-        <v>71.40000000000001</v>
+        <v>28.1</v>
       </c>
       <c r="J55" s="32" t="n">
-        <v>8.6</v>
+        <v>16.9</v>
       </c>
       <c r="K55" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="L55" s="21" t="inlineStr">
-        <is>
-          <t>おおむね予定どおり</t>
+      <c r="L55" s="33" t="inlineStr">
+        <is>
+          <t>前倒し</t>
         </is>
       </c>
       <c r="M55" s="19" t="inlineStr">
         <is>
-          <t>**令和7年度の様式4が全て0で未入力。また基金保有額が令和4年度末120百万円から令和5年度末12百万円へ1桁減っており、取崩実績か入力誤りかの確認が要る**</t>
+          <t>**目指すべき姿の内容の確定（決定11）。公立小野町地方綜合病院・田村郡医師会等との調整が要る。**あわせて在宅医療・介護連携推進事業の実施状況（相談窓口の運営、多職種研修、情報共有ツール）</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="19" t="inlineStr">
         <is>
-          <t>P6 骨子案</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="B56" s="20" t="inlineStr">
         <is>
-          <t>6-1</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="C56" s="19" t="inlineStr">
         <is>
-          <t>骨子案の作成</t>
+          <t>見える化 優先度C分野の出力</t>
         </is>
       </c>
       <c r="D56" s="20" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="E56" s="20" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F56" s="20" t="inlineStr">
@@ -7021,16 +7021,16 @@
         </is>
       </c>
       <c r="H56" s="32" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="I56" s="32" t="n">
-        <v>63.2</v>
+        <v>37.8</v>
       </c>
       <c r="J56" s="32" t="n">
-        <v>16.8</v>
+        <v>17.2</v>
       </c>
       <c r="K56" s="20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L56" s="33" t="inlineStr">
         <is>
@@ -7039,24 +7039,24 @@
       </c>
       <c r="M56" s="19" t="inlineStr">
         <is>
-          <t>実績データによる数値の確定</t>
+          <t>**残るのは医療提供体制・リハビリ提供体制の出力。見える化システムへのアクセスは確保できている（9月28日に推計が通った）**</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="19" t="inlineStr">
         <is>
-          <t>P8 素案</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="B57" s="20" t="inlineStr">
         <is>
-          <t>8-8</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="C57" s="19" t="inlineStr">
         <is>
-          <t>在宅医療・介護連携の目指すべき姿の設定</t>
+          <t>認定者数の異常値の検証</t>
         </is>
       </c>
       <c r="D57" s="20" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="E57" s="20" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F57" s="20" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G57" s="23" t="inlineStr">
@@ -7080,16 +7080,16 @@
         </is>
       </c>
       <c r="H57" s="32" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="I57" s="32" t="n">
-        <v>28.1</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J57" s="32" t="n">
-        <v>16.9</v>
+        <v>18.6</v>
       </c>
       <c r="K57" s="20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L57" s="33" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="M57" s="19" t="inlineStr">
         <is>
-          <t>**目指すべき姿の内容の確定（決定11）。公立小野町地方綜合病院・田村郡医師会等との調整が要る。**あわせて在宅医療・介護連携推進事業の実施状況（相談窓口の運営、多職種研修、情報共有ツール）</t>
+          <t>**「令和7年8〜9月に計上方法の変更がなかったか」に論点が絞られた。町外施設入所者の帰属、住所地特例、国保連の集計定義のいずれか**</t>
         </is>
       </c>
     </row>
@@ -7110,12 +7110,12 @@
       </c>
       <c r="B58" s="20" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>2-12</t>
         </is>
       </c>
       <c r="C58" s="19" t="inlineStr">
         <is>
-          <t>見える化 優先度C分野の出力</t>
+          <t>総合事業の実施状況の分析</t>
         </is>
       </c>
       <c r="D58" s="20" t="inlineStr">
@@ -7130,7 +7130,7 @@
       </c>
       <c r="F58" s="20" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G58" s="23" t="inlineStr">
@@ -7139,16 +7139,16 @@
         </is>
       </c>
       <c r="H58" s="32" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="I58" s="32" t="n">
-        <v>37.8</v>
+        <v>56.7</v>
       </c>
       <c r="J58" s="32" t="n">
-        <v>17.2</v>
+        <v>28.3</v>
       </c>
       <c r="K58" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L58" s="33" t="inlineStr">
         <is>
@@ -7157,29 +7157,29 @@
       </c>
       <c r="M58" s="19" t="inlineStr">
         <is>
-          <t>**残るのは医療提供体制・リハビリ提供体制の出力。見える化システムへのアクセスは確保できている（9月28日に推計が通った）**</t>
+          <t>**ワークシートに載る実施状況調査の回答は、従前相当サービスの利用者数がほとんど空欄で、実人数と延べ人数が同じ年があり、サービスBの人数が408→24→150→24人と激しく振れている。時系列として使えないため、町の控え（平成29年度〜令和6年度）との突合が要る**　**10月1日に通いの場の図を作成（f48）。**見える化は平成28年度以降0か所、調査では13.8％が年に数回以上参加。食い違いの解明は町の事業実績待ち</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="19" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P10 完成・納品</t>
         </is>
       </c>
       <c r="B59" s="20" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>10-4</t>
         </is>
       </c>
       <c r="C59" s="19" t="inlineStr">
         <is>
-          <t>認定者数の異常値の検証</t>
+          <t>概要版の構成案</t>
         </is>
       </c>
       <c r="D59" s="20" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E59" s="20" t="inlineStr">
@@ -7192,22 +7192,22 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="G59" s="23" t="inlineStr">
-        <is>
-          <t>進行中</t>
+      <c r="G59" s="21" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H59" s="32" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I59" s="32" t="n">
         <v>71.40000000000001</v>
       </c>
       <c r="J59" s="32" t="n">
-        <v>18.6</v>
+        <v>28.6</v>
       </c>
       <c r="K59" s="20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L59" s="33" t="inlineStr">
         <is>
@@ -7216,29 +7216,29 @@
       </c>
       <c r="M59" s="19" t="inlineStr">
         <is>
-          <t>**「令和7年8〜9月に計上方法の変更がなかったか」に論点が絞られた。町外施設入所者の帰属、住所地特例、国保連の集計定義のいずれか**</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="19" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P8 素案</t>
         </is>
       </c>
       <c r="B60" s="20" t="inlineStr">
         <is>
-          <t>2-12</t>
+          <t>8-7</t>
         </is>
       </c>
       <c r="C60" s="19" t="inlineStr">
         <is>
-          <t>総合事業の実施状況の分析</t>
+          <t>介護給付適正化計画の位置づけと主要3事業の定量目標</t>
         </is>
       </c>
       <c r="D60" s="20" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E60" s="20" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="F60" s="20" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G60" s="23" t="inlineStr">
@@ -7257,13 +7257,13 @@
         </is>
       </c>
       <c r="H60" s="32" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="I60" s="32" t="n">
-        <v>56.7</v>
+        <v>28.1</v>
       </c>
       <c r="J60" s="32" t="n">
-        <v>28.3</v>
+        <v>31.9</v>
       </c>
       <c r="K60" s="20" t="n">
         <v>3</v>
@@ -7275,29 +7275,29 @@
       </c>
       <c r="M60" s="19" t="inlineStr">
         <is>
-          <t>**ワークシートに載る実施状況調査の回答は、従前相当サービスの利用者数がほとんど空欄で、実人数と延べ人数が同じ年があり、サービスBの人数が408→24→150→24人と激しく振れている。時系列として使えないため、町の控え（平成29年度〜令和6年度）との突合が要る**　**10月1日に通いの場の図を作成（f48）。**見える化は平成28年度以降0か所、調査では13.8％が年に数回以上参加。食い違いの解明は町の事業実績待ち</t>
+          <t>**位置づけの決定（決定9）と、ケアプラン点検の点検件数の目標（決定10）。****あわせて、令和6年度のケアプラン点検の実施件数（0点の理由が件数の少なさか報告していないことかの特定）と、要介護認定の適正化の実施内容（認定調査の委託の有無と点検件数）が要る**</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="19" t="inlineStr">
         <is>
-          <t>P8 素案</t>
+          <t>P7 推計・算定</t>
         </is>
       </c>
       <c r="B61" s="20" t="inlineStr">
         <is>
-          <t>8-7</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="C61" s="19" t="inlineStr">
         <is>
-          <t>介護給付適正化計画の位置づけと主要3事業の定量目標</t>
+          <t>被保険者数・認定者数の推計</t>
         </is>
       </c>
       <c r="D61" s="20" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E61" s="20" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="F61" s="20" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G61" s="23" t="inlineStr">
@@ -7316,16 +7316,16 @@
         </is>
       </c>
       <c r="H61" s="32" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="I61" s="32" t="n">
-        <v>28.1</v>
+        <v>56.7</v>
       </c>
       <c r="J61" s="32" t="n">
-        <v>31.9</v>
+        <v>33.3</v>
       </c>
       <c r="K61" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L61" s="33" t="inlineStr">
         <is>
@@ -7334,24 +7334,24 @@
       </c>
       <c r="M61" s="19" t="inlineStr">
         <is>
-          <t>**位置づけの決定（決定9）と、ケアプラン点検の点検件数の目標（決定10）。****あわせて、令和6年度のケアプラン点検の実施件数（0点の理由が件数の少なさか報告していないことかの特定）と、要介護認定の適正化の実施内容（認定調査の委託の有無と点検件数）が要る**</t>
+          <t>**認定率をどの水準で置くか（令和7年度実績か、計上変更前の令和6年度水準か）。2-4の確認結果しだいで前提が変わる。**あわせて、認定率の分子に第2号被保険者の認定者を含むかを見える化の画面で確認する（確認事項No.125）</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="19" t="inlineStr">
         <is>
-          <t>P7 推計・算定</t>
+          <t>P5 第9期の評価</t>
         </is>
       </c>
       <c r="B62" s="20" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="C62" s="19" t="inlineStr">
         <is>
-          <t>被保険者数・認定者数の推計</t>
+          <t>成果目標の達成状況の確定</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
@@ -7384,7 +7384,7 @@
         <v>33.3</v>
       </c>
       <c r="K62" s="20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L62" s="33" t="inlineStr">
         <is>
@@ -7393,24 +7393,24 @@
       </c>
       <c r="M62" s="19" t="inlineStr">
         <is>
-          <t>**認定率をどの水準で置くか（令和7年度実績か、計上変更前の令和6年度水準か）。2-4の確認結果しだいで前提が変わる。**あわせて、認定率の分子に第2号被保険者の認定者を含むかを見える化の画面で確認する（確認事項No.125）</t>
+          <t>**地域支援事業費の実績（年報 様式4の令和6・7年度が未入力。依頼票H3）と成果指標の現状値（H1〜H15）。令和8年度は年度途中のため令和9年夏の年報を待つ**</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="19" t="inlineStr">
         <is>
-          <t>P5 第9期の評価</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="B63" s="20" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>2-13</t>
         </is>
       </c>
       <c r="C63" s="19" t="inlineStr">
         <is>
-          <t>成果目標の達成状況の確定</t>
+          <t>地域分析・検討シートの記入案の作成</t>
         </is>
       </c>
       <c r="D63" s="20" t="inlineStr">
@@ -7443,7 +7443,7 @@
         <v>33.3</v>
       </c>
       <c r="K63" s="20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L63" s="33" t="inlineStr">
         <is>
@@ -7452,39 +7452,39 @@
       </c>
       <c r="M63" s="19" t="inlineStr">
         <is>
-          <t>**地域支援事業費の実績（年報 様式4の令和6・7年度が未入力。依頼票H3）と成果指標の現状値（H1〜H15）。令和8年度は年度途中のため令和9年夏の年報を待つ**</t>
+          <t>**町の確定稿への記入は町が行う。記入案のうち通いの場・総合事業に関する記述は2-6・2-12と同じデータ待ちで、町の事業実績が入ると書き換えが要る**</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="19" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P9 意見聴取</t>
         </is>
       </c>
       <c r="B64" s="20" t="inlineStr">
         <is>
-          <t>2-13</t>
+          <t>9-3</t>
         </is>
       </c>
       <c r="C64" s="19" t="inlineStr">
         <is>
-          <t>地域分析・検討シートの記入案の作成</t>
+          <t>協議会 第2回（骨子案・見込量・保険料・成果指標）</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E64" s="20" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="F64" s="20" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="G64" s="23" t="inlineStr">
@@ -7493,13 +7493,13 @@
         </is>
       </c>
       <c r="H64" s="32" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="I64" s="32" t="n">
-        <v>56.7</v>
+        <v>0</v>
       </c>
       <c r="J64" s="32" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="K64" s="20" t="n">
         <v>2</v>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="M64" s="19" t="inlineStr">
         <is>
-          <t>**町の確定稿への記入は町が行う。記入案のうち通いの場・総合事業に関する記述は2-6・2-12と同じデータ待ちで、町の事業実績が入ると書き換えが要る**</t>
+          <t>開催日の確定（案Aなら11月27日が期限）</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
     <row r="80">
       <c r="A80" s="34" t="inlineStr">
         <is>
-          <t>加重の実績進捗率 70.3％　対　予定進捗率 54.9％　乖離 +15.4ポイント</t>
+          <t>加重の実績進捗率 70.7％　対　予定進捗率 54.8％　乖離 +16.0ポイント</t>
         </is>
       </c>
     </row>
@@ -8365,14 +8365,14 @@
     <row r="83">
       <c r="A83" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">　おおむね予定どおり 46件</t>
+          <t xml:space="preserve">　おおむね予定どおり 44件</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">　前倒し 23件</t>
+          <t xml:space="preserve">　前倒し 25件</t>
         </is>
       </c>
     </row>
@@ -13147,25 +13147,25 @@
           <t>2026-11</t>
         </is>
       </c>
-      <c r="K58" s="27" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K58" s="23" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="L58" s="22" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M58" s="23" t="n">
         <v>2</v>
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>骨子案第3版・成果指標目標値案は作成済み</t>
+          <t>**資料を作成済み（令和8年10月6日・08_協議会資料）。骨子案 第4版・見込量・保険料の2案・成果指標の目標値の置き方の3案。数値は算定モジュールから引いており、算定が変われば資料も変わる**</t>
         </is>
       </c>
       <c r="O58" s="19" t="inlineStr">
         <is>
-          <t>P7の完了、開催日の確定</t>
+          <t>開催日の確定（案Aなら11月27日が期限）</t>
         </is>
       </c>
       <c r="P58" s="24" t="n"/>
@@ -13873,7 +13873,7 @@
       </c>
       <c r="J67" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="K67" s="21" t="inlineStr">
@@ -13889,7 +13889,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>計画策定業務設計書 第2章（02_キックオフ・業務計画）</t>
+          <t>計画策定業務設計書 第2章（02_キックオフ・業務計画）。**令和8年10月6日に図の割付まで決めた（10_納品・印刷）。既存の図6点を頁に割り付け、作る図2点の作成時期を11月とした**</t>
         </is>
       </c>
       <c r="O67" s="19" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>構成案は作成済み</t>
+          <t>**構成案とページ割り・図の割付は作成済み。**1頁あたりの分量を文字数で見積もり、8頁に収まることを確かめた</t>
         </is>
       </c>
       <c r="O68" s="19" t="inlineStr">
